--- a/Informes/Gantt Vehículo Autónomo.xlsx
+++ b/Informes/Gantt Vehículo Autónomo.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a31f0271d0b8797b/Desktop/Proyecto Ingenieria/INFORMES/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="603" documentId="8_{A2B61D2F-08BD-40F5-ACC5-C73775A42AA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B01CF647-A38A-4CCB-BEE8-E7219F639B33}"/>
+  <xr:revisionPtr revIDLastSave="646" documentId="8_{A2B61D2F-08BD-40F5-ACC5-C73775A42AA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9ABC49D0-F1D8-47A4-B507-E0F67FD6380F}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Diagrama de Gantt" sheetId="14" r:id="rId1"/>
@@ -18,11 +18,11 @@
     <sheet name="Listado de Componentes" sheetId="16" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="Display_Week" localSheetId="0">'Diagrama de Gantt'!$Q$2</definedName>
+    <definedName name="Display_Week" localSheetId="0">'Diagrama de Gantt'!$S$2</definedName>
     <definedName name="Display_Week">#REF!</definedName>
-    <definedName name="Project_Start" localSheetId="0">'Diagrama de Gantt'!$Q$1</definedName>
+    <definedName name="Project_Start" localSheetId="0">'Diagrama de Gantt'!$S$1</definedName>
     <definedName name="Project_Start">#REF!</definedName>
-    <definedName name="task_end" localSheetId="0">'Diagrama de Gantt'!$F1</definedName>
+    <definedName name="task_end" localSheetId="0">'Diagrama de Gantt'!$H1</definedName>
     <definedName name="task_progress" localSheetId="0">'Diagrama de Gantt'!$C1</definedName>
     <definedName name="task_start" localSheetId="0">'Diagrama de Gantt'!$D1</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Diagrama de Gantt'!$4:$6</definedName>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="101">
   <si>
     <t>Vehículo Autónomo para marcado de Layout</t>
   </si>
@@ -123,9 +123,6 @@
     <t>Interfaz</t>
   </si>
   <si>
-    <t>Conexión PC / ESP32 por Bluetooth</t>
-  </si>
-  <si>
     <t>Convertir CAD a coordenadas</t>
   </si>
   <si>
@@ -135,9 +132,6 @@
     <t>Sistema de marcado</t>
   </si>
   <si>
-    <t>Bomba de tinta</t>
-  </si>
-  <si>
     <t xml:space="preserve">Diseño de tanque de tinta </t>
   </si>
   <si>
@@ -346,6 +340,18 @@
   </si>
   <si>
     <t>Bomba persitaltica</t>
+  </si>
+  <si>
+    <t>HORAS ESTIMADAS</t>
+  </si>
+  <si>
+    <t>HORAS REALES</t>
+  </si>
+  <si>
+    <t>Conexión PC / ESP32 por WIFI</t>
+  </si>
+  <si>
+    <t>Bomba de tinta (montaje, conexión)</t>
   </si>
 </sst>
 </file>
@@ -1192,7 +1198,7 @@
     </xf>
     <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="192">
+  <cellXfs count="196">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1680,27 +1686,20 @@
     <xf numFmtId="0" fontId="9" fillId="18" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="15" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="15" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="11" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="11" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="11" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="11" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="40" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="8" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1717,23 +1716,42 @@
     <xf numFmtId="167" fontId="15" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="167" fontId="15" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="15" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="11" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="11" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="11" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="11" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="18" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="20" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="15" fillId="17" borderId="21" xfId="10" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="19" borderId="21" xfId="10" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="11" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="11" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="14">
@@ -1876,25 +1894,6 @@
       </border>
     </dxf>
     <dxf>
-      <numFmt numFmtId="169" formatCode="_-[$$-409]* #,##0_ ;_-[$$-409]* \-#,##0\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="169" formatCode="_-[$$-409]* #,##0_ ;_-[$$-409]* \-#,##0\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="169" formatCode="_-[$$-409]* #,##0_ ;_-[$$-409]* \-#,##0\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="169" formatCode="_-[$$-409]* #,##0_ ;_-[$$-409]* \-#,##0\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
@@ -1991,6 +1990,25 @@
         <top/>
         <bottom/>
       </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="169" formatCode="_-[$$-409]* #,##0_ ;_-[$$-409]* \-#,##0\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="169" formatCode="_-[$$-409]* #,##0_ ;_-[$$-409]* \-#,##0\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="169" formatCode="_-[$$-409]* #,##0_ ;_-[$$-409]* \-#,##0\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="169" formatCode="_-[$$-409]* #,##0_ ;_-[$$-409]* \-#,##0\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <border>
@@ -2190,7 +2208,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{7B046895-9170-4AC6-8C65-BF0F2537217B}" name="Tabla3" displayName="Tabla3" ref="C2:F23" totalsRowShown="0" headerRowDxfId="19">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{7B046895-9170-4AC6-8C65-BF0F2537217B}" name="Tabla3" displayName="Tabla3" ref="C2:F23" totalsRowShown="0" headerRowDxfId="13">
   <autoFilter ref="C2:F23" xr:uid="{7B046895-9170-4AC6-8C65-BF0F2537217B}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -2198,10 +2216,10 @@
     <filterColumn colId="3" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{677FC96E-7F25-4A06-87E3-922FDD41B915}" name="Tarea" dataDxfId="18"/>
-    <tableColumn id="2" xr3:uid="{58277187-363E-428B-A83B-BC14DB987A6B}" name="Horas estimadas" dataDxfId="17"/>
-    <tableColumn id="3" xr3:uid="{488EC91C-90C1-4FC4-A305-62832539CD69}" name="Horas reales" dataDxfId="16"/>
-    <tableColumn id="4" xr3:uid="{C0DE1A19-3FEF-4849-899B-C98251D2724D}" name="Diferencia" dataDxfId="15">
+    <tableColumn id="1" xr3:uid="{677FC96E-7F25-4A06-87E3-922FDD41B915}" name="Tarea" dataDxfId="12"/>
+    <tableColumn id="2" xr3:uid="{58277187-363E-428B-A83B-BC14DB987A6B}" name="Horas estimadas" dataDxfId="11"/>
+    <tableColumn id="3" xr3:uid="{488EC91C-90C1-4FC4-A305-62832539CD69}" name="Horas reales" dataDxfId="10"/>
+    <tableColumn id="4" xr3:uid="{C0DE1A19-3FEF-4849-899B-C98251D2724D}" name="Diferencia" dataDxfId="9">
       <calculatedColumnFormula>Tabla3[[#This Row],[Horas reales]]-Tabla3[[#This Row],[Horas estimadas]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -2220,12 +2238,12 @@
     <filterColumn colId="5" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{45ACA5F6-477D-42B6-B421-4AEE018B4E81}" name="Nombre" totalsRowLabel="Total" dataDxfId="14"/>
-    <tableColumn id="2" xr3:uid="{CDC2B791-5EFB-4C87-AAD3-192DBB5C19D6}" name="Descripción" dataDxfId="13"/>
+    <tableColumn id="1" xr3:uid="{45ACA5F6-477D-42B6-B421-4AEE018B4E81}" name="Nombre" totalsRowLabel="Total" dataDxfId="19"/>
+    <tableColumn id="2" xr3:uid="{CDC2B791-5EFB-4C87-AAD3-192DBB5C19D6}" name="Descripción" dataDxfId="18"/>
     <tableColumn id="3" xr3:uid="{95A5BD7C-444C-4C6D-BE74-E16B3FFFEE8E}" name="Cantidad"/>
     <tableColumn id="4" xr3:uid="{FF7F68A1-0DEA-4B69-8384-B1FE22AD9958}" name="Proveedor"/>
-    <tableColumn id="5" xr3:uid="{63F8E491-A0B5-4A72-A3FF-8221530F268B}" name="Precio unitario" totalsRowLabel=" $ARS " dataDxfId="12" totalsRowDxfId="10"/>
-    <tableColumn id="6" xr3:uid="{1E275AE4-1059-4BEF-B3F7-9BB27037631B}" name="Total" totalsRowFunction="sum" dataDxfId="11" totalsRowDxfId="9"/>
+    <tableColumn id="5" xr3:uid="{63F8E491-A0B5-4A72-A3FF-8221530F268B}" name="Precio unitario" totalsRowLabel=" $ARS " dataDxfId="17" totalsRowDxfId="16"/>
+    <tableColumn id="6" xr3:uid="{1E275AE4-1059-4BEF-B3F7-9BB27037631B}" name="Total" totalsRowFunction="sum" dataDxfId="15" totalsRowDxfId="14"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium4" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2437,39 +2455,39 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:BL36"/>
+  <dimension ref="A1:BN36"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.58203125" defaultRowHeight="30" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="40.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.58203125" customWidth="1"/>
     <col min="3" max="3" width="10.58203125" customWidth="1"/>
-    <col min="4" max="5" width="10.58203125" style="2" customWidth="1"/>
-    <col min="6" max="6" width="10.58203125" customWidth="1"/>
-    <col min="7" max="7" width="2.58203125" customWidth="1"/>
-    <col min="8" max="8" width="144.58203125" hidden="1" customWidth="1"/>
-    <col min="9" max="9" width="2.83203125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="2.58203125" bestFit="1" customWidth="1"/>
-    <col min="11" max="18" width="2.83203125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="3.08203125" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="2.83203125" bestFit="1" customWidth="1"/>
-    <col min="21" max="29" width="3.08203125" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="2.83203125" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="2.33203125" bestFit="1" customWidth="1"/>
-    <col min="33" max="37" width="2.08203125" bestFit="1" customWidth="1"/>
-    <col min="38" max="39" width="2.33203125" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="2.83203125" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="2.58203125" bestFit="1" customWidth="1"/>
-    <col min="42" max="49" width="2.83203125" bestFit="1" customWidth="1"/>
-    <col min="50" max="50" width="3.08203125" bestFit="1" customWidth="1"/>
-    <col min="51" max="51" width="2.83203125" bestFit="1" customWidth="1"/>
-    <col min="52" max="60" width="3.08203125" bestFit="1" customWidth="1"/>
-    <col min="61" max="61" width="1.83203125" bestFit="1" customWidth="1"/>
-    <col min="62" max="63" width="2.08203125" bestFit="1" customWidth="1"/>
-    <col min="64" max="64" width="3.08203125" bestFit="1" customWidth="1"/>
-    <col min="65" max="65" width="2.58203125" customWidth="1"/>
+    <col min="4" max="7" width="10.58203125" style="2" customWidth="1"/>
+    <col min="8" max="8" width="10.58203125" customWidth="1"/>
+    <col min="9" max="9" width="2.58203125" customWidth="1"/>
+    <col min="10" max="10" width="144.58203125" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="2.83203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="2.58203125" bestFit="1" customWidth="1"/>
+    <col min="13" max="20" width="2.83203125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="3.08203125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="2.83203125" bestFit="1" customWidth="1"/>
+    <col min="23" max="31" width="3.08203125" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="2.83203125" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="2.33203125" bestFit="1" customWidth="1"/>
+    <col min="35" max="39" width="2.08203125" bestFit="1" customWidth="1"/>
+    <col min="40" max="41" width="2.33203125" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="2.83203125" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="2.58203125" bestFit="1" customWidth="1"/>
+    <col min="44" max="51" width="2.83203125" bestFit="1" customWidth="1"/>
+    <col min="52" max="52" width="3.08203125" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="2.83203125" bestFit="1" customWidth="1"/>
+    <col min="54" max="62" width="3.08203125" bestFit="1" customWidth="1"/>
+    <col min="63" max="63" width="1.83203125" bestFit="1" customWidth="1"/>
+    <col min="64" max="65" width="2.08203125" bestFit="1" customWidth="1"/>
+    <col min="66" max="66" width="3.08203125" bestFit="1" customWidth="1"/>
+    <col min="67" max="67" width="2.58203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:64" ht="90" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="1" spans="1:66" ht="90" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A1" s="70" t="s">
         <v>0</v>
       </c>
@@ -2477,32 +2495,34 @@
       <c r="C1" s="11"/>
       <c r="D1" s="12"/>
       <c r="E1" s="12"/>
-      <c r="F1" s="13"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="179" t="s">
+      <c r="F1" s="12"/>
+      <c r="G1" s="12"/>
+      <c r="H1" s="13"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="176" t="s">
         <v>1</v>
       </c>
-      <c r="J1" s="180"/>
-      <c r="K1" s="180"/>
-      <c r="L1" s="180"/>
-      <c r="M1" s="180"/>
-      <c r="N1" s="180"/>
-      <c r="O1" s="180"/>
-      <c r="P1" s="16"/>
-      <c r="Q1" s="181">
+      <c r="L1" s="177"/>
+      <c r="M1" s="177"/>
+      <c r="N1" s="177"/>
+      <c r="O1" s="177"/>
+      <c r="P1" s="177"/>
+      <c r="Q1" s="177"/>
+      <c r="R1" s="16"/>
+      <c r="S1" s="178">
         <v>46244</v>
       </c>
-      <c r="R1" s="182"/>
-      <c r="S1" s="182"/>
-      <c r="T1" s="182"/>
-      <c r="U1" s="182"/>
-      <c r="V1" s="182"/>
-      <c r="W1" s="182"/>
-      <c r="X1" s="182"/>
-      <c r="Y1" s="182"/>
-      <c r="Z1" s="182"/>
-    </row>
-    <row r="2" spans="1:64" ht="30" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="T1" s="179"/>
+      <c r="U1" s="179"/>
+      <c r="V1" s="179"/>
+      <c r="W1" s="179"/>
+      <c r="X1" s="179"/>
+      <c r="Y1" s="179"/>
+      <c r="Z1" s="179"/>
+      <c r="AA1" s="179"/>
+      <c r="AB1" s="179"/>
+    </row>
+    <row r="2" spans="1:66" ht="30" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A2" s="71" t="s">
         <v>2</v>
       </c>
@@ -2512,610 +2532,624 @@
       <c r="C2" s="14"/>
       <c r="D2" s="15"/>
       <c r="E2" s="15"/>
-      <c r="F2" s="14"/>
-      <c r="I2" s="179" t="s">
+      <c r="F2" s="15"/>
+      <c r="G2" s="15"/>
+      <c r="H2" s="14"/>
+      <c r="K2" s="176" t="s">
         <v>4</v>
       </c>
-      <c r="J2" s="180"/>
-      <c r="K2" s="180"/>
-      <c r="L2" s="180"/>
-      <c r="M2" s="180"/>
-      <c r="N2" s="180"/>
-      <c r="O2" s="180"/>
-      <c r="P2" s="16"/>
-      <c r="Q2" s="183">
+      <c r="L2" s="177"/>
+      <c r="M2" s="177"/>
+      <c r="N2" s="177"/>
+      <c r="O2" s="177"/>
+      <c r="P2" s="177"/>
+      <c r="Q2" s="177"/>
+      <c r="R2" s="16"/>
+      <c r="S2" s="180">
         <v>2</v>
       </c>
-      <c r="R2" s="184"/>
-      <c r="S2" s="184"/>
-      <c r="T2" s="184"/>
-      <c r="U2" s="184"/>
-      <c r="V2" s="184"/>
-      <c r="W2" s="184"/>
-      <c r="X2" s="184"/>
-      <c r="Y2" s="184"/>
-      <c r="Z2" s="184"/>
-    </row>
-    <row r="3" spans="1:64" s="18" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T2" s="181"/>
+      <c r="U2" s="181"/>
+      <c r="V2" s="181"/>
+      <c r="W2" s="181"/>
+      <c r="X2" s="181"/>
+      <c r="Y2" s="181"/>
+      <c r="Z2" s="181"/>
+      <c r="AA2" s="181"/>
+      <c r="AB2" s="181"/>
+    </row>
+    <row r="3" spans="1:66" s="18" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="17"/>
       <c r="C3" s="19"/>
       <c r="D3" s="20"/>
       <c r="E3" s="20"/>
-    </row>
-    <row r="4" spans="1:64" s="18" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F3" s="20"/>
+      <c r="G3" s="20"/>
+    </row>
+    <row r="4" spans="1:66" s="18" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="21"/>
       <c r="D4" s="22"/>
       <c r="E4" s="22"/>
-      <c r="I4" s="185">
-        <f>I5</f>
+      <c r="F4" s="22"/>
+      <c r="G4" s="22"/>
+      <c r="K4" s="182">
+        <f>K5</f>
         <v>46251</v>
       </c>
-      <c r="J4" s="171"/>
-      <c r="K4" s="171"/>
-      <c r="L4" s="171"/>
-      <c r="M4" s="171"/>
-      <c r="N4" s="171"/>
-      <c r="O4" s="171"/>
-      <c r="P4" s="171">
-        <f>P5</f>
+      <c r="L4" s="183"/>
+      <c r="M4" s="183"/>
+      <c r="N4" s="183"/>
+      <c r="O4" s="183"/>
+      <c r="P4" s="183"/>
+      <c r="Q4" s="183"/>
+      <c r="R4" s="183">
+        <f>R5</f>
         <v>46258</v>
       </c>
-      <c r="Q4" s="171"/>
-      <c r="R4" s="171"/>
-      <c r="S4" s="171"/>
-      <c r="T4" s="171"/>
-      <c r="U4" s="171"/>
-      <c r="V4" s="171"/>
-      <c r="W4" s="171">
-        <f>W5</f>
+      <c r="S4" s="183"/>
+      <c r="T4" s="183"/>
+      <c r="U4" s="183"/>
+      <c r="V4" s="183"/>
+      <c r="W4" s="183"/>
+      <c r="X4" s="183"/>
+      <c r="Y4" s="183">
+        <f>Y5</f>
         <v>46265</v>
       </c>
-      <c r="X4" s="171"/>
-      <c r="Y4" s="171"/>
-      <c r="Z4" s="171"/>
-      <c r="AA4" s="171"/>
-      <c r="AB4" s="171"/>
-      <c r="AC4" s="171"/>
-      <c r="AD4" s="171">
-        <f>AD5</f>
+      <c r="Z4" s="183"/>
+      <c r="AA4" s="183"/>
+      <c r="AB4" s="183"/>
+      <c r="AC4" s="183"/>
+      <c r="AD4" s="183"/>
+      <c r="AE4" s="183"/>
+      <c r="AF4" s="183">
+        <f>AF5</f>
         <v>46272</v>
       </c>
-      <c r="AE4" s="171"/>
-      <c r="AF4" s="171"/>
-      <c r="AG4" s="171"/>
-      <c r="AH4" s="171"/>
-      <c r="AI4" s="171"/>
-      <c r="AJ4" s="171"/>
-      <c r="AK4" s="171">
-        <f>AK5</f>
+      <c r="AG4" s="183"/>
+      <c r="AH4" s="183"/>
+      <c r="AI4" s="183"/>
+      <c r="AJ4" s="183"/>
+      <c r="AK4" s="183"/>
+      <c r="AL4" s="183"/>
+      <c r="AM4" s="183">
+        <f>AM5</f>
         <v>46279</v>
       </c>
-      <c r="AL4" s="171"/>
-      <c r="AM4" s="171"/>
-      <c r="AN4" s="171"/>
-      <c r="AO4" s="171"/>
-      <c r="AP4" s="171"/>
-      <c r="AQ4" s="171"/>
-      <c r="AR4" s="171">
-        <f>AR5</f>
+      <c r="AN4" s="183"/>
+      <c r="AO4" s="183"/>
+      <c r="AP4" s="183"/>
+      <c r="AQ4" s="183"/>
+      <c r="AR4" s="183"/>
+      <c r="AS4" s="183"/>
+      <c r="AT4" s="183">
+        <f>AT5</f>
         <v>46286</v>
       </c>
-      <c r="AS4" s="171"/>
-      <c r="AT4" s="171"/>
-      <c r="AU4" s="171"/>
-      <c r="AV4" s="171"/>
-      <c r="AW4" s="171"/>
-      <c r="AX4" s="171"/>
-      <c r="AY4" s="171">
-        <f>AY5</f>
+      <c r="AU4" s="183"/>
+      <c r="AV4" s="183"/>
+      <c r="AW4" s="183"/>
+      <c r="AX4" s="183"/>
+      <c r="AY4" s="183"/>
+      <c r="AZ4" s="183"/>
+      <c r="BA4" s="183">
+        <f>BA5</f>
         <v>46293</v>
       </c>
-      <c r="AZ4" s="171"/>
-      <c r="BA4" s="171"/>
-      <c r="BB4" s="171"/>
-      <c r="BC4" s="171"/>
-      <c r="BD4" s="171"/>
-      <c r="BE4" s="171"/>
-      <c r="BF4" s="171">
-        <f>BF5</f>
+      <c r="BB4" s="183"/>
+      <c r="BC4" s="183"/>
+      <c r="BD4" s="183"/>
+      <c r="BE4" s="183"/>
+      <c r="BF4" s="183"/>
+      <c r="BG4" s="183"/>
+      <c r="BH4" s="183">
+        <f>BH5</f>
         <v>46300</v>
       </c>
-      <c r="BG4" s="171"/>
-      <c r="BH4" s="171"/>
-      <c r="BI4" s="171"/>
-      <c r="BJ4" s="171"/>
-      <c r="BK4" s="171"/>
-      <c r="BL4" s="172"/>
-    </row>
-    <row r="5" spans="1:64" s="18" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="173" t="s">
+      <c r="BI4" s="183"/>
+      <c r="BJ4" s="183"/>
+      <c r="BK4" s="183"/>
+      <c r="BL4" s="183"/>
+      <c r="BM4" s="183"/>
+      <c r="BN4" s="184"/>
+    </row>
+    <row r="5" spans="1:66" s="18" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="185" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="175" t="s">
+      <c r="B5" s="187" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="177" t="s">
+      <c r="C5" s="189" t="s">
         <v>7</v>
       </c>
-      <c r="D5" s="177" t="s">
+      <c r="D5" s="189" t="s">
         <v>8</v>
       </c>
-      <c r="E5" s="177" t="s">
+      <c r="E5" s="189" t="s">
         <v>9</v>
       </c>
-      <c r="F5" s="177" t="s">
+      <c r="F5" s="189" t="s">
         <v>10</v>
       </c>
-      <c r="I5" s="23">
+      <c r="G5" s="194" t="s">
+        <v>97</v>
+      </c>
+      <c r="H5" s="194" t="s">
+        <v>98</v>
+      </c>
+      <c r="K5" s="23">
         <f>Project_Start-WEEKDAY(Project_Start,1)+2+7*(Display_Week-1)</f>
         <v>46251</v>
       </c>
-      <c r="J5" s="23">
-        <f>I5+1</f>
+      <c r="L5" s="23">
+        <f>K5+1</f>
         <v>46252</v>
       </c>
-      <c r="K5" s="23">
-        <f t="shared" ref="K5:AX5" si="0">J5+1</f>
+      <c r="M5" s="23">
+        <f t="shared" ref="M5:AZ5" si="0">L5+1</f>
         <v>46253</v>
       </c>
-      <c r="L5" s="23">
+      <c r="N5" s="23">
         <f t="shared" si="0"/>
         <v>46254</v>
       </c>
-      <c r="M5" s="23">
+      <c r="O5" s="23">
         <f t="shared" si="0"/>
         <v>46255</v>
       </c>
-      <c r="N5" s="23">
+      <c r="P5" s="23">
         <f t="shared" si="0"/>
         <v>46256</v>
       </c>
-      <c r="O5" s="24">
+      <c r="Q5" s="24">
         <f t="shared" si="0"/>
         <v>46257</v>
       </c>
-      <c r="P5" s="25">
-        <f>O5+1</f>
+      <c r="R5" s="25">
+        <f>Q5+1</f>
         <v>46258</v>
       </c>
-      <c r="Q5" s="23">
-        <f>P5+1</f>
+      <c r="S5" s="23">
+        <f>R5+1</f>
         <v>46259</v>
       </c>
-      <c r="R5" s="23">
+      <c r="T5" s="23">
         <f t="shared" si="0"/>
         <v>46260</v>
       </c>
-      <c r="S5" s="23">
+      <c r="U5" s="23">
         <f t="shared" si="0"/>
         <v>46261</v>
       </c>
-      <c r="T5" s="23">
+      <c r="V5" s="23">
         <f t="shared" si="0"/>
         <v>46262</v>
       </c>
-      <c r="U5" s="23">
+      <c r="W5" s="23">
         <f t="shared" si="0"/>
         <v>46263</v>
       </c>
-      <c r="V5" s="24">
+      <c r="X5" s="24">
         <f t="shared" si="0"/>
         <v>46264</v>
       </c>
-      <c r="W5" s="25">
-        <f>V5+1</f>
+      <c r="Y5" s="25">
+        <f>X5+1</f>
         <v>46265</v>
       </c>
-      <c r="X5" s="23">
-        <f>W5+1</f>
+      <c r="Z5" s="23">
+        <f>Y5+1</f>
         <v>46266</v>
       </c>
-      <c r="Y5" s="23">
+      <c r="AA5" s="23">
         <f t="shared" si="0"/>
         <v>46267</v>
       </c>
-      <c r="Z5" s="23">
+      <c r="AB5" s="23">
         <f t="shared" si="0"/>
         <v>46268</v>
       </c>
-      <c r="AA5" s="23">
+      <c r="AC5" s="23">
         <f t="shared" si="0"/>
         <v>46269</v>
       </c>
-      <c r="AB5" s="23">
+      <c r="AD5" s="23">
         <f t="shared" si="0"/>
         <v>46270</v>
       </c>
-      <c r="AC5" s="24">
+      <c r="AE5" s="24">
         <f t="shared" si="0"/>
         <v>46271</v>
       </c>
-      <c r="AD5" s="25">
-        <f>AC5+1</f>
+      <c r="AF5" s="25">
+        <f>AE5+1</f>
         <v>46272</v>
       </c>
-      <c r="AE5" s="23">
-        <f>AD5+1</f>
+      <c r="AG5" s="23">
+        <f>AF5+1</f>
         <v>46273</v>
       </c>
-      <c r="AF5" s="23">
+      <c r="AH5" s="23">
         <f t="shared" si="0"/>
         <v>46274</v>
       </c>
-      <c r="AG5" s="23">
+      <c r="AI5" s="23">
         <f t="shared" si="0"/>
         <v>46275</v>
       </c>
-      <c r="AH5" s="23">
+      <c r="AJ5" s="23">
         <f t="shared" si="0"/>
         <v>46276</v>
       </c>
-      <c r="AI5" s="23">
+      <c r="AK5" s="23">
         <f t="shared" si="0"/>
         <v>46277</v>
       </c>
-      <c r="AJ5" s="24">
+      <c r="AL5" s="24">
         <f t="shared" si="0"/>
         <v>46278</v>
       </c>
-      <c r="AK5" s="25">
-        <f>AJ5+1</f>
+      <c r="AM5" s="25">
+        <f>AL5+1</f>
         <v>46279</v>
       </c>
-      <c r="AL5" s="23">
-        <f>AK5+1</f>
+      <c r="AN5" s="23">
+        <f>AM5+1</f>
         <v>46280</v>
       </c>
-      <c r="AM5" s="23">
+      <c r="AO5" s="23">
         <f t="shared" si="0"/>
         <v>46281</v>
       </c>
-      <c r="AN5" s="23">
+      <c r="AP5" s="23">
         <f t="shared" si="0"/>
         <v>46282</v>
       </c>
-      <c r="AO5" s="23">
+      <c r="AQ5" s="23">
         <f t="shared" si="0"/>
         <v>46283</v>
       </c>
-      <c r="AP5" s="23">
+      <c r="AR5" s="23">
         <f t="shared" si="0"/>
         <v>46284</v>
       </c>
-      <c r="AQ5" s="24">
+      <c r="AS5" s="24">
         <f t="shared" si="0"/>
         <v>46285</v>
       </c>
-      <c r="AR5" s="25">
-        <f>AQ5+1</f>
+      <c r="AT5" s="25">
+        <f>AS5+1</f>
         <v>46286</v>
       </c>
-      <c r="AS5" s="23">
-        <f>AR5+1</f>
+      <c r="AU5" s="23">
+        <f>AT5+1</f>
         <v>46287</v>
       </c>
-      <c r="AT5" s="23">
+      <c r="AV5" s="23">
         <f t="shared" si="0"/>
         <v>46288</v>
       </c>
-      <c r="AU5" s="23">
+      <c r="AW5" s="23">
         <f t="shared" si="0"/>
         <v>46289</v>
       </c>
-      <c r="AV5" s="23">
+      <c r="AX5" s="23">
         <f t="shared" si="0"/>
         <v>46290</v>
       </c>
-      <c r="AW5" s="23">
+      <c r="AY5" s="23">
         <f t="shared" si="0"/>
         <v>46291</v>
       </c>
-      <c r="AX5" s="24">
+      <c r="AZ5" s="24">
         <f t="shared" si="0"/>
         <v>46292</v>
       </c>
-      <c r="AY5" s="25">
-        <f>AX5+1</f>
+      <c r="BA5" s="25">
+        <f>AZ5+1</f>
         <v>46293</v>
       </c>
-      <c r="AZ5" s="23">
-        <f>AY5+1</f>
+      <c r="BB5" s="23">
+        <f>BA5+1</f>
         <v>46294</v>
       </c>
-      <c r="BA5" s="23">
-        <f t="shared" ref="BA5:BE5" si="1">AZ5+1</f>
+      <c r="BC5" s="23">
+        <f t="shared" ref="BC5:BG5" si="1">BB5+1</f>
         <v>46295</v>
       </c>
-      <c r="BB5" s="23">
+      <c r="BD5" s="23">
         <f t="shared" si="1"/>
         <v>46296</v>
       </c>
-      <c r="BC5" s="23">
+      <c r="BE5" s="23">
         <f t="shared" si="1"/>
         <v>46297</v>
       </c>
-      <c r="BD5" s="23">
+      <c r="BF5" s="23">
         <f t="shared" si="1"/>
         <v>46298</v>
       </c>
-      <c r="BE5" s="24">
+      <c r="BG5" s="24">
         <f t="shared" si="1"/>
         <v>46299</v>
       </c>
-      <c r="BF5" s="25">
-        <f>BE5+1</f>
+      <c r="BH5" s="25">
+        <f>BG5+1</f>
         <v>46300</v>
       </c>
-      <c r="BG5" s="23">
-        <f>BF5+1</f>
+      <c r="BI5" s="23">
+        <f>BH5+1</f>
         <v>46301</v>
       </c>
-      <c r="BH5" s="23">
-        <f t="shared" ref="BH5:BL5" si="2">BG5+1</f>
+      <c r="BJ5" s="23">
+        <f t="shared" ref="BJ5:BN5" si="2">BI5+1</f>
         <v>46302</v>
       </c>
-      <c r="BI5" s="23">
+      <c r="BK5" s="23">
         <f t="shared" si="2"/>
         <v>46303</v>
       </c>
-      <c r="BJ5" s="23">
+      <c r="BL5" s="23">
         <f t="shared" si="2"/>
         <v>46304</v>
       </c>
-      <c r="BK5" s="23">
+      <c r="BM5" s="23">
         <f t="shared" si="2"/>
         <v>46305</v>
       </c>
-      <c r="BL5" s="23">
+      <c r="BN5" s="23">
         <f t="shared" si="2"/>
         <v>46306</v>
       </c>
     </row>
-    <row r="6" spans="1:64" s="18" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="174"/>
-      <c r="B6" s="176"/>
-      <c r="C6" s="176"/>
-      <c r="D6" s="176"/>
-      <c r="E6" s="178"/>
-      <c r="F6" s="176"/>
-      <c r="I6" s="26" t="str">
-        <f t="shared" ref="I6:BL6" si="3">LEFT(TEXT(I5,"ddd"),1)</f>
+    <row r="6" spans="1:66" s="18" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="186"/>
+      <c r="B6" s="188"/>
+      <c r="C6" s="188"/>
+      <c r="D6" s="188"/>
+      <c r="E6" s="190"/>
+      <c r="F6" s="188"/>
+      <c r="G6" s="195"/>
+      <c r="H6" s="195"/>
+      <c r="K6" s="26" t="str">
+        <f t="shared" ref="K6:BN6" si="3">LEFT(TEXT(K5,"ddd"),1)</f>
         <v>l</v>
       </c>
-      <c r="J6" s="27" t="str">
+      <c r="L6" s="27" t="str">
         <f t="shared" si="3"/>
         <v>m</v>
       </c>
-      <c r="K6" s="27" t="str">
+      <c r="M6" s="27" t="str">
         <f t="shared" si="3"/>
         <v>m</v>
       </c>
-      <c r="L6" s="27" t="str">
+      <c r="N6" s="27" t="str">
         <f t="shared" si="3"/>
         <v>j</v>
       </c>
-      <c r="M6" s="27" t="str">
+      <c r="O6" s="27" t="str">
         <f t="shared" si="3"/>
         <v>v</v>
       </c>
-      <c r="N6" s="27" t="str">
+      <c r="P6" s="27" t="str">
         <f t="shared" si="3"/>
         <v>s</v>
       </c>
-      <c r="O6" s="27" t="str">
+      <c r="Q6" s="27" t="str">
         <f t="shared" si="3"/>
         <v>d</v>
       </c>
-      <c r="P6" s="27" t="str">
+      <c r="R6" s="27" t="str">
         <f t="shared" si="3"/>
         <v>l</v>
       </c>
-      <c r="Q6" s="27" t="str">
+      <c r="S6" s="27" t="str">
         <f t="shared" si="3"/>
         <v>m</v>
       </c>
-      <c r="R6" s="27" t="str">
+      <c r="T6" s="27" t="str">
         <f t="shared" si="3"/>
         <v>m</v>
       </c>
-      <c r="S6" s="27" t="str">
+      <c r="U6" s="27" t="str">
         <f t="shared" si="3"/>
         <v>j</v>
       </c>
-      <c r="T6" s="27" t="str">
+      <c r="V6" s="27" t="str">
         <f t="shared" si="3"/>
         <v>v</v>
       </c>
-      <c r="U6" s="27" t="str">
+      <c r="W6" s="27" t="str">
         <f t="shared" si="3"/>
         <v>s</v>
       </c>
-      <c r="V6" s="27" t="str">
+      <c r="X6" s="27" t="str">
         <f t="shared" si="3"/>
         <v>d</v>
       </c>
-      <c r="W6" s="27" t="str">
+      <c r="Y6" s="27" t="str">
         <f t="shared" si="3"/>
         <v>l</v>
       </c>
-      <c r="X6" s="27" t="str">
+      <c r="Z6" s="27" t="str">
         <f t="shared" si="3"/>
         <v>m</v>
       </c>
-      <c r="Y6" s="27" t="str">
+      <c r="AA6" s="27" t="str">
         <f t="shared" si="3"/>
         <v>m</v>
       </c>
-      <c r="Z6" s="27" t="str">
+      <c r="AB6" s="27" t="str">
         <f t="shared" si="3"/>
         <v>j</v>
       </c>
-      <c r="AA6" s="27" t="str">
+      <c r="AC6" s="27" t="str">
         <f t="shared" si="3"/>
         <v>v</v>
       </c>
-      <c r="AB6" s="27" t="str">
+      <c r="AD6" s="27" t="str">
         <f t="shared" si="3"/>
         <v>s</v>
       </c>
-      <c r="AC6" s="27" t="str">
+      <c r="AE6" s="27" t="str">
         <f t="shared" si="3"/>
         <v>d</v>
       </c>
-      <c r="AD6" s="27" t="str">
+      <c r="AF6" s="27" t="str">
         <f t="shared" si="3"/>
         <v>l</v>
       </c>
-      <c r="AE6" s="27" t="str">
+      <c r="AG6" s="27" t="str">
         <f t="shared" si="3"/>
         <v>m</v>
       </c>
-      <c r="AF6" s="27" t="str">
+      <c r="AH6" s="27" t="str">
         <f t="shared" si="3"/>
         <v>m</v>
       </c>
-      <c r="AG6" s="27" t="str">
+      <c r="AI6" s="27" t="str">
         <f t="shared" si="3"/>
         <v>j</v>
       </c>
-      <c r="AH6" s="27" t="str">
+      <c r="AJ6" s="27" t="str">
         <f t="shared" si="3"/>
         <v>v</v>
       </c>
-      <c r="AI6" s="27" t="str">
+      <c r="AK6" s="27" t="str">
         <f t="shared" si="3"/>
         <v>s</v>
       </c>
-      <c r="AJ6" s="27" t="str">
+      <c r="AL6" s="27" t="str">
         <f t="shared" si="3"/>
         <v>d</v>
       </c>
-      <c r="AK6" s="27" t="str">
+      <c r="AM6" s="27" t="str">
         <f t="shared" si="3"/>
         <v>l</v>
       </c>
-      <c r="AL6" s="27" t="str">
+      <c r="AN6" s="27" t="str">
         <f t="shared" si="3"/>
         <v>m</v>
       </c>
-      <c r="AM6" s="27" t="str">
+      <c r="AO6" s="27" t="str">
         <f t="shared" si="3"/>
         <v>m</v>
       </c>
-      <c r="AN6" s="27" t="str">
+      <c r="AP6" s="27" t="str">
         <f t="shared" si="3"/>
         <v>j</v>
       </c>
-      <c r="AO6" s="27" t="str">
+      <c r="AQ6" s="27" t="str">
         <f t="shared" si="3"/>
         <v>v</v>
       </c>
-      <c r="AP6" s="27" t="str">
+      <c r="AR6" s="27" t="str">
         <f t="shared" si="3"/>
         <v>s</v>
       </c>
-      <c r="AQ6" s="27" t="str">
+      <c r="AS6" s="27" t="str">
         <f t="shared" si="3"/>
         <v>d</v>
       </c>
-      <c r="AR6" s="27" t="str">
+      <c r="AT6" s="27" t="str">
         <f t="shared" si="3"/>
         <v>l</v>
       </c>
-      <c r="AS6" s="27" t="str">
+      <c r="AU6" s="27" t="str">
         <f t="shared" si="3"/>
         <v>m</v>
       </c>
-      <c r="AT6" s="27" t="str">
+      <c r="AV6" s="27" t="str">
         <f t="shared" si="3"/>
         <v>m</v>
       </c>
-      <c r="AU6" s="27" t="str">
+      <c r="AW6" s="27" t="str">
         <f t="shared" si="3"/>
         <v>j</v>
       </c>
-      <c r="AV6" s="27" t="str">
+      <c r="AX6" s="27" t="str">
         <f t="shared" si="3"/>
         <v>v</v>
       </c>
-      <c r="AW6" s="27" t="str">
+      <c r="AY6" s="27" t="str">
         <f t="shared" si="3"/>
         <v>s</v>
       </c>
-      <c r="AX6" s="27" t="str">
+      <c r="AZ6" s="27" t="str">
         <f t="shared" si="3"/>
         <v>d</v>
       </c>
-      <c r="AY6" s="27" t="str">
+      <c r="BA6" s="27" t="str">
         <f t="shared" si="3"/>
         <v>l</v>
       </c>
-      <c r="AZ6" s="27" t="str">
+      <c r="BB6" s="27" t="str">
         <f t="shared" si="3"/>
         <v>m</v>
       </c>
-      <c r="BA6" s="27" t="str">
+      <c r="BC6" s="27" t="str">
         <f t="shared" si="3"/>
         <v>m</v>
       </c>
-      <c r="BB6" s="27" t="str">
+      <c r="BD6" s="27" t="str">
         <f t="shared" si="3"/>
         <v>j</v>
       </c>
-      <c r="BC6" s="27" t="str">
+      <c r="BE6" s="27" t="str">
         <f t="shared" si="3"/>
         <v>v</v>
       </c>
-      <c r="BD6" s="27" t="str">
+      <c r="BF6" s="27" t="str">
         <f t="shared" si="3"/>
         <v>s</v>
       </c>
-      <c r="BE6" s="27" t="str">
+      <c r="BG6" s="27" t="str">
         <f t="shared" si="3"/>
         <v>d</v>
       </c>
-      <c r="BF6" s="27" t="str">
+      <c r="BH6" s="27" t="str">
         <f t="shared" si="3"/>
         <v>l</v>
       </c>
-      <c r="BG6" s="27" t="str">
+      <c r="BI6" s="27" t="str">
         <f t="shared" si="3"/>
         <v>m</v>
       </c>
-      <c r="BH6" s="27" t="str">
+      <c r="BJ6" s="27" t="str">
         <f t="shared" si="3"/>
         <v>m</v>
       </c>
-      <c r="BI6" s="27" t="str">
+      <c r="BK6" s="27" t="str">
         <f t="shared" si="3"/>
         <v>j</v>
       </c>
-      <c r="BJ6" s="27" t="str">
+      <c r="BL6" s="27" t="str">
         <f t="shared" si="3"/>
         <v>v</v>
       </c>
-      <c r="BK6" s="27" t="str">
+      <c r="BM6" s="27" t="str">
         <f t="shared" si="3"/>
         <v>s</v>
       </c>
-      <c r="BL6" s="28" t="str">
+      <c r="BN6" s="28" t="str">
         <f t="shared" si="3"/>
         <v>d</v>
       </c>
     </row>
-    <row r="7" spans="1:64" s="18" customFormat="1" ht="30" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:66" s="18" customFormat="1" ht="30" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="29"/>
       <c r="B7" s="30"/>
       <c r="C7" s="29"/>
       <c r="D7" s="29"/>
       <c r="E7" s="29"/>
       <c r="F7" s="29"/>
-      <c r="H7" s="18" t="str">
+      <c r="G7" s="29"/>
+      <c r="H7" s="29"/>
+      <c r="J7" s="18" t="str">
         <f>IF(OR(ISBLANK(task_start),ISBLANK(task_end)),"",task_end-task_start+1)</f>
         <v/>
       </c>
-      <c r="I7" s="31"/>
-      <c r="J7" s="31"/>
       <c r="K7" s="31"/>
       <c r="L7" s="31"/>
       <c r="M7" s="31"/>
@@ -3170,8 +3204,10 @@
       <c r="BJ7" s="31"/>
       <c r="BK7" s="31"/>
       <c r="BL7" s="31"/>
-    </row>
-    <row r="8" spans="1:64" s="38" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="BM7" s="31"/>
+      <c r="BN7" s="31"/>
+    </row>
+    <row r="8" spans="1:66" s="38" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="32" t="s">
         <v>11</v>
       </c>
@@ -3180,13 +3216,13 @@
       <c r="D8" s="35"/>
       <c r="E8" s="35"/>
       <c r="F8" s="36"/>
-      <c r="G8" s="9"/>
-      <c r="H8" s="5" t="str">
-        <f t="shared" ref="H8:H33" si="4">IF(OR(ISBLANK(task_start),ISBLANK(task_end)),"",task_end-task_start+1)</f>
+      <c r="G8" s="35"/>
+      <c r="H8" s="35"/>
+      <c r="I8" s="9"/>
+      <c r="J8" s="5" t="str">
+        <f t="shared" ref="J8:J33" si="4">IF(OR(ISBLANK(task_start),ISBLANK(task_end)),"",task_end-task_start+1)</f>
         <v/>
       </c>
-      <c r="I8" s="37"/>
-      <c r="J8" s="37"/>
       <c r="K8" s="37"/>
       <c r="L8" s="37"/>
       <c r="M8" s="37"/>
@@ -3241,8 +3277,10 @@
       <c r="BJ8" s="37"/>
       <c r="BK8" s="37"/>
       <c r="BL8" s="37"/>
-    </row>
-    <row r="9" spans="1:64" s="38" customFormat="1" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="BM8" s="37"/>
+      <c r="BN8" s="37"/>
+    </row>
+    <row r="9" spans="1:66" s="38" customFormat="1" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="142" t="s">
         <v>12</v>
       </c>
@@ -3262,13 +3300,17 @@
         <f>D9+E9</f>
         <v>46246</v>
       </c>
-      <c r="G9" s="9"/>
-      <c r="H9" s="5">
+      <c r="G9" s="87">
+        <v>2</v>
+      </c>
+      <c r="H9" s="87">
+        <v>2</v>
+      </c>
+      <c r="I9" s="9"/>
+      <c r="J9" s="5">
         <f t="shared" si="4"/>
-        <v>3</v>
-      </c>
-      <c r="I9" s="41"/>
-      <c r="J9" s="41"/>
+        <v>-46241</v>
+      </c>
       <c r="K9" s="41"/>
       <c r="L9" s="41"/>
       <c r="M9" s="41"/>
@@ -3323,8 +3365,10 @@
       <c r="BJ9" s="41"/>
       <c r="BK9" s="41"/>
       <c r="BL9" s="41"/>
-    </row>
-    <row r="10" spans="1:64" s="38" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="BM9" s="41"/>
+      <c r="BN9" s="41"/>
+    </row>
+    <row r="10" spans="1:66" s="38" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="165" t="s">
         <v>14</v>
       </c>
@@ -3342,16 +3386,20 @@
         <v>40</v>
       </c>
       <c r="F10" s="73">
-        <f t="shared" ref="F10" si="5">D10+E10</f>
+        <f>D10+E10</f>
         <v>46286</v>
       </c>
-      <c r="G10" s="9"/>
-      <c r="H10" s="5">
+      <c r="G10" s="87">
+        <v>20</v>
+      </c>
+      <c r="H10" s="87">
+        <v>8</v>
+      </c>
+      <c r="I10" s="9"/>
+      <c r="J10" s="5">
         <f t="shared" si="4"/>
-        <v>41</v>
-      </c>
-      <c r="I10" s="41"/>
-      <c r="J10" s="41"/>
+        <v>-46237</v>
+      </c>
       <c r="K10" s="41"/>
       <c r="L10" s="41"/>
       <c r="M10" s="41"/>
@@ -3362,10 +3410,10 @@
       <c r="R10" s="41"/>
       <c r="S10" s="41"/>
       <c r="T10" s="41"/>
-      <c r="U10" s="44"/>
-      <c r="V10" s="44"/>
-      <c r="W10" s="41"/>
-      <c r="X10" s="41"/>
+      <c r="U10" s="41"/>
+      <c r="V10" s="41"/>
+      <c r="W10" s="44"/>
+      <c r="X10" s="44"/>
       <c r="Y10" s="41"/>
       <c r="Z10" s="41"/>
       <c r="AA10" s="41"/>
@@ -3406,8 +3454,10 @@
       <c r="BJ10" s="41"/>
       <c r="BK10" s="41"/>
       <c r="BL10" s="41"/>
-    </row>
-    <row r="11" spans="1:64" s="38" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="BM10" s="41"/>
+      <c r="BN10" s="41"/>
+    </row>
+    <row r="11" spans="1:66" s="38" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="45" t="s">
         <v>16</v>
       </c>
@@ -3416,13 +3466,15 @@
       <c r="D11" s="75"/>
       <c r="E11" s="91"/>
       <c r="F11" s="76"/>
-      <c r="G11" s="9"/>
-      <c r="H11" s="5" t="str">
+      <c r="G11" s="91"/>
+      <c r="H11" s="91"/>
+      <c r="I11" s="9"/>
+      <c r="J11" s="5" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
-    <row r="12" spans="1:64" s="38" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:66" s="38" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="143" t="s">
         <v>17</v>
       </c>
@@ -3442,13 +3494,17 @@
         <f>D12+E12</f>
         <v>46273</v>
       </c>
-      <c r="G12" s="9"/>
-      <c r="H12" s="5">
+      <c r="G12" s="89">
+        <v>12</v>
+      </c>
+      <c r="H12" s="89">
+        <v>6</v>
+      </c>
+      <c r="I12" s="9"/>
+      <c r="J12" s="5">
         <f t="shared" si="4"/>
-        <v>8</v>
-      </c>
-      <c r="I12" s="41"/>
-      <c r="J12" s="41"/>
+        <v>-46259</v>
+      </c>
       <c r="K12" s="41"/>
       <c r="L12" s="41"/>
       <c r="M12" s="41"/>
@@ -3503,8 +3559,10 @@
       <c r="BJ12" s="41"/>
       <c r="BK12" s="41"/>
       <c r="BL12" s="41"/>
-    </row>
-    <row r="13" spans="1:64" s="38" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="BM12" s="41"/>
+      <c r="BN12" s="41"/>
+    </row>
+    <row r="13" spans="1:66" s="38" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="143" t="s">
         <v>18</v>
       </c>
@@ -3520,17 +3578,21 @@
       <c r="E13" s="89">
         <v>40</v>
       </c>
-      <c r="F13" s="77">
+      <c r="F13" s="89">
         <f>D13+E13</f>
         <v>46306</v>
       </c>
-      <c r="G13" s="9"/>
-      <c r="H13" s="5">
+      <c r="G13" s="89">
+        <v>30</v>
+      </c>
+      <c r="H13" s="89">
+        <v>12</v>
+      </c>
+      <c r="I13" s="9"/>
+      <c r="J13" s="5">
         <f t="shared" si="4"/>
-        <v>41</v>
-      </c>
-      <c r="I13" s="41"/>
-      <c r="J13" s="41"/>
+        <v>-46253</v>
+      </c>
       <c r="K13" s="41"/>
       <c r="L13" s="41"/>
       <c r="M13" s="41"/>
@@ -3541,10 +3603,10 @@
       <c r="R13" s="41"/>
       <c r="S13" s="41"/>
       <c r="T13" s="41"/>
-      <c r="U13" s="44"/>
-      <c r="V13" s="44"/>
-      <c r="W13" s="41"/>
-      <c r="X13" s="41"/>
+      <c r="U13" s="41"/>
+      <c r="V13" s="41"/>
+      <c r="W13" s="44"/>
+      <c r="X13" s="44"/>
       <c r="Y13" s="41"/>
       <c r="Z13" s="41"/>
       <c r="AA13" s="41"/>
@@ -3585,8 +3647,10 @@
       <c r="BJ13" s="41"/>
       <c r="BK13" s="41"/>
       <c r="BL13" s="41"/>
-    </row>
-    <row r="14" spans="1:64" s="38" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="BM13" s="41"/>
+      <c r="BN13" s="41"/>
+    </row>
+    <row r="14" spans="1:66" s="38" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="168" t="s">
         <v>20</v>
       </c>
@@ -3602,14 +3666,18 @@
       <c r="E14" s="104">
         <v>14</v>
       </c>
-      <c r="F14" s="77">
+      <c r="F14" s="103">
         <f>D14+E14</f>
         <v>46279</v>
       </c>
-      <c r="G14" s="9"/>
-      <c r="H14" s="5"/>
-      <c r="I14" s="53"/>
-      <c r="J14" s="53"/>
+      <c r="G14" s="104">
+        <v>12</v>
+      </c>
+      <c r="H14" s="104">
+        <v>1</v>
+      </c>
+      <c r="I14" s="9"/>
+      <c r="J14" s="5"/>
       <c r="K14" s="53"/>
       <c r="L14" s="53"/>
       <c r="M14" s="53"/>
@@ -3620,10 +3688,10 @@
       <c r="R14" s="53"/>
       <c r="S14" s="53"/>
       <c r="T14" s="53"/>
-      <c r="U14" s="169"/>
-      <c r="V14" s="169"/>
-      <c r="W14" s="53"/>
-      <c r="X14" s="53"/>
+      <c r="U14" s="53"/>
+      <c r="V14" s="53"/>
+      <c r="W14" s="169"/>
+      <c r="X14" s="169"/>
       <c r="Y14" s="53"/>
       <c r="Z14" s="53"/>
       <c r="AA14" s="53"/>
@@ -3664,8 +3732,10 @@
       <c r="BJ14" s="53"/>
       <c r="BK14" s="53"/>
       <c r="BL14" s="53"/>
-    </row>
-    <row r="15" spans="1:64" s="38" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="BM14" s="53"/>
+      <c r="BN14" s="53"/>
+    </row>
+    <row r="15" spans="1:66" s="38" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="50" t="s">
         <v>21</v>
       </c>
@@ -3674,13 +3744,13 @@
       <c r="D15" s="78"/>
       <c r="E15" s="92"/>
       <c r="F15" s="79"/>
-      <c r="G15" s="9"/>
-      <c r="H15" s="5" t="str">
+      <c r="G15" s="92"/>
+      <c r="H15" s="92"/>
+      <c r="I15" s="9"/>
+      <c r="J15" s="5" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="I15" s="53"/>
-      <c r="J15" s="53"/>
       <c r="K15" s="53"/>
       <c r="L15" s="53"/>
       <c r="M15" s="53"/>
@@ -3735,8 +3805,10 @@
       <c r="BJ15" s="53"/>
       <c r="BK15" s="53"/>
       <c r="BL15" s="53"/>
-    </row>
-    <row r="16" spans="1:64" s="38" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="BM15" s="53"/>
+      <c r="BN15" s="53"/>
+    </row>
+    <row r="16" spans="1:66" s="38" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="54" t="s">
         <v>22</v>
       </c>
@@ -3756,10 +3828,12 @@
         <f>D16+E16</f>
         <v>46299</v>
       </c>
-      <c r="G16" s="9"/>
-      <c r="H16" s="5"/>
-      <c r="I16" s="41"/>
-      <c r="J16" s="41"/>
+      <c r="G16" s="90">
+        <v>12</v>
+      </c>
+      <c r="H16" s="90"/>
+      <c r="I16" s="9"/>
+      <c r="J16" s="5"/>
       <c r="K16" s="41"/>
       <c r="L16" s="41"/>
       <c r="M16" s="41"/>
@@ -3814,8 +3888,10 @@
       <c r="BJ16" s="41"/>
       <c r="BK16" s="41"/>
       <c r="BL16" s="41"/>
-    </row>
-    <row r="17" spans="1:64" s="38" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="BM16" s="41"/>
+      <c r="BN16" s="41"/>
+    </row>
+    <row r="17" spans="1:66" s="38" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="86" t="s">
         <v>23</v>
       </c>
@@ -3824,10 +3900,10 @@
       <c r="D17" s="85"/>
       <c r="E17" s="93"/>
       <c r="F17" s="85"/>
-      <c r="G17" s="9"/>
-      <c r="H17" s="5"/>
-      <c r="I17" s="59"/>
-      <c r="J17" s="59"/>
+      <c r="G17" s="93"/>
+      <c r="H17" s="93"/>
+      <c r="I17" s="9"/>
+      <c r="J17" s="5"/>
       <c r="K17" s="59"/>
       <c r="L17" s="59"/>
       <c r="M17" s="59"/>
@@ -3882,10 +3958,12 @@
       <c r="BJ17" s="59"/>
       <c r="BK17" s="59"/>
       <c r="BL17" s="59"/>
-    </row>
-    <row r="18" spans="1:64" s="38" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="BM17" s="59"/>
+      <c r="BN17" s="59"/>
+    </row>
+    <row r="18" spans="1:66" s="38" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="110" t="s">
-        <v>24</v>
+        <v>99</v>
       </c>
       <c r="B18" s="163" t="s">
         <v>13</v>
@@ -3903,10 +3981,14 @@
         <f>D18+E18</f>
         <v>46258</v>
       </c>
-      <c r="G18" s="9"/>
-      <c r="H18" s="5"/>
-      <c r="I18" s="59"/>
-      <c r="J18" s="59"/>
+      <c r="G18" s="113">
+        <v>4</v>
+      </c>
+      <c r="H18" s="113">
+        <v>4</v>
+      </c>
+      <c r="I18" s="9"/>
+      <c r="J18" s="5"/>
       <c r="K18" s="59"/>
       <c r="L18" s="59"/>
       <c r="M18" s="59"/>
@@ -3961,10 +4043,12 @@
       <c r="BJ18" s="59"/>
       <c r="BK18" s="59"/>
       <c r="BL18" s="59"/>
-    </row>
-    <row r="19" spans="1:64" s="38" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="BM18" s="59"/>
+      <c r="BN18" s="59"/>
+    </row>
+    <row r="19" spans="1:66" s="38" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="114" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B19" s="164" t="s">
         <v>13</v>
@@ -3979,13 +4063,17 @@
         <v>5</v>
       </c>
       <c r="F19" s="112">
-        <f t="shared" ref="F19:F20" si="6">D19+E19</f>
+        <f>D19+E19</f>
         <v>46258</v>
       </c>
-      <c r="G19" s="9"/>
-      <c r="H19" s="5"/>
-      <c r="I19" s="59"/>
-      <c r="J19" s="59"/>
+      <c r="G19" s="192">
+        <v>4</v>
+      </c>
+      <c r="H19" s="192">
+        <v>4</v>
+      </c>
+      <c r="I19" s="9"/>
+      <c r="J19" s="5"/>
       <c r="K19" s="59"/>
       <c r="L19" s="59"/>
       <c r="M19" s="59"/>
@@ -4040,10 +4128,12 @@
       <c r="BJ19" s="59"/>
       <c r="BK19" s="59"/>
       <c r="BL19" s="59"/>
-    </row>
-    <row r="20" spans="1:64" s="38" customFormat="1" ht="41.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="BM19" s="59"/>
+      <c r="BN19" s="59"/>
+    </row>
+    <row r="20" spans="1:66" s="38" customFormat="1" ht="41.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="166" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B20" s="152"/>
       <c r="C20" s="153">
@@ -4056,13 +4146,13 @@
         <v>0</v>
       </c>
       <c r="F20" s="156">
-        <f t="shared" si="6"/>
+        <f>D20+E20</f>
         <v>46293</v>
       </c>
-      <c r="G20" s="9"/>
-      <c r="H20" s="5"/>
-      <c r="I20" s="59"/>
-      <c r="J20" s="59"/>
+      <c r="G20" s="193"/>
+      <c r="H20" s="193"/>
+      <c r="I20" s="9"/>
+      <c r="J20" s="5"/>
       <c r="K20" s="59"/>
       <c r="L20" s="59"/>
       <c r="M20" s="59"/>
@@ -4082,9 +4172,9 @@
       <c r="AA20" s="59"/>
       <c r="AB20" s="59"/>
       <c r="AC20" s="59"/>
-      <c r="AD20"/>
+      <c r="AD20" s="59"/>
       <c r="AE20" s="59"/>
-      <c r="AF20" s="59"/>
+      <c r="AF20"/>
       <c r="AG20" s="59"/>
       <c r="AH20" s="59"/>
       <c r="AI20" s="59"/>
@@ -4117,20 +4207,22 @@
       <c r="BJ20" s="59"/>
       <c r="BK20" s="59"/>
       <c r="BL20" s="59"/>
-    </row>
-    <row r="21" spans="1:64" s="38" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="BM20" s="59"/>
+      <c r="BN20" s="59"/>
+    </row>
+    <row r="21" spans="1:66" s="38" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="100" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B21" s="95"/>
       <c r="C21" s="96"/>
       <c r="D21" s="97"/>
       <c r="E21" s="98"/>
       <c r="F21" s="97"/>
-      <c r="G21" s="9"/>
-      <c r="H21" s="5"/>
-      <c r="I21" s="59"/>
-      <c r="J21" s="59"/>
+      <c r="G21" s="98"/>
+      <c r="H21" s="98"/>
+      <c r="I21" s="9"/>
+      <c r="J21" s="5"/>
       <c r="K21" s="59"/>
       <c r="L21" s="59"/>
       <c r="M21" s="59"/>
@@ -4185,10 +4277,12 @@
       <c r="BJ21" s="59"/>
       <c r="BK21" s="59"/>
       <c r="BL21" s="59"/>
-    </row>
-    <row r="22" spans="1:64" s="38" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="BM21" s="59"/>
+      <c r="BN21" s="59"/>
+    </row>
+    <row r="22" spans="1:66" s="38" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="118" t="s">
-        <v>28</v>
+        <v>100</v>
       </c>
       <c r="B22" s="119" t="s">
         <v>15</v>
@@ -4206,10 +4300,12 @@
         <f>E22+D22</f>
         <v>46313</v>
       </c>
-      <c r="G22" s="9"/>
-      <c r="H22" s="5"/>
-      <c r="I22" s="59"/>
-      <c r="J22" s="59"/>
+      <c r="G22" s="122">
+        <v>4</v>
+      </c>
+      <c r="H22" s="122"/>
+      <c r="I22" s="9"/>
+      <c r="J22" s="5"/>
       <c r="K22" s="59"/>
       <c r="L22" s="59"/>
       <c r="M22" s="59"/>
@@ -4264,10 +4360,12 @@
       <c r="BJ22" s="59"/>
       <c r="BK22" s="59"/>
       <c r="BL22" s="59"/>
-    </row>
-    <row r="23" spans="1:64" s="38" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="BM22" s="59"/>
+      <c r="BN22" s="59"/>
+    </row>
+    <row r="23" spans="1:66" s="38" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="118" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B23" s="119" t="s">
         <v>15</v>
@@ -4282,13 +4380,15 @@
         <v>3</v>
       </c>
       <c r="F23" s="123">
-        <f t="shared" ref="F23:F24" si="7">E23+D23</f>
+        <f>E23+D23</f>
         <v>46317</v>
       </c>
-      <c r="G23" s="9"/>
-      <c r="H23" s="5"/>
-      <c r="I23" s="59"/>
-      <c r="J23" s="59"/>
+      <c r="G23" s="122">
+        <v>4</v>
+      </c>
+      <c r="H23" s="122"/>
+      <c r="I23" s="9"/>
+      <c r="J23" s="5"/>
       <c r="K23" s="59"/>
       <c r="L23" s="59"/>
       <c r="M23" s="59"/>
@@ -4343,10 +4443,12 @@
       <c r="BJ23" s="59"/>
       <c r="BK23" s="59"/>
       <c r="BL23" s="59"/>
-    </row>
-    <row r="24" spans="1:64" s="38" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="BM23" s="59"/>
+      <c r="BN23" s="59"/>
+    </row>
+    <row r="24" spans="1:66" s="38" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="118" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B24" s="119" t="s">
         <v>15</v>
@@ -4361,13 +4463,15 @@
         <v>3</v>
       </c>
       <c r="F24" s="123">
-        <f t="shared" si="7"/>
+        <f>E24+D24</f>
         <v>46321</v>
       </c>
-      <c r="G24" s="9"/>
-      <c r="H24" s="5"/>
-      <c r="I24" s="59"/>
-      <c r="J24" s="59"/>
+      <c r="G24" s="122">
+        <v>4</v>
+      </c>
+      <c r="H24" s="122"/>
+      <c r="I24" s="9"/>
+      <c r="J24" s="5"/>
       <c r="K24" s="59"/>
       <c r="L24" s="59"/>
       <c r="M24" s="59"/>
@@ -4422,20 +4526,22 @@
       <c r="BJ24" s="59"/>
       <c r="BK24" s="59"/>
       <c r="BL24" s="59"/>
-    </row>
-    <row r="25" spans="1:64" s="38" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="BM24" s="59"/>
+      <c r="BN24" s="59"/>
+    </row>
+    <row r="25" spans="1:66" s="38" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" s="105" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B25" s="106"/>
       <c r="C25" s="107"/>
       <c r="D25" s="108"/>
       <c r="E25" s="109"/>
       <c r="F25" s="108"/>
-      <c r="G25" s="9"/>
-      <c r="H25" s="5"/>
-      <c r="I25" s="59"/>
-      <c r="J25" s="59"/>
+      <c r="G25" s="109"/>
+      <c r="H25" s="109"/>
+      <c r="I25" s="9"/>
+      <c r="J25" s="5"/>
       <c r="K25" s="59"/>
       <c r="L25" s="59"/>
       <c r="M25" s="59"/>
@@ -4490,10 +4596,12 @@
       <c r="BJ25" s="59"/>
       <c r="BK25" s="59"/>
       <c r="BL25" s="59"/>
-    </row>
-    <row r="26" spans="1:64" s="38" customFormat="1" ht="38.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="BM25" s="59"/>
+      <c r="BN25" s="59"/>
+    </row>
+    <row r="26" spans="1:66" s="38" customFormat="1" ht="38.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="167" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B26" s="158"/>
       <c r="C26" s="159"/>
@@ -4507,10 +4615,10 @@
         <f>E26+D26</f>
         <v>46321</v>
       </c>
-      <c r="G26" s="9"/>
-      <c r="H26" s="5"/>
-      <c r="I26" s="59"/>
-      <c r="J26" s="59"/>
+      <c r="G26" s="161"/>
+      <c r="H26" s="161"/>
+      <c r="I26" s="9"/>
+      <c r="J26" s="5"/>
       <c r="K26" s="59"/>
       <c r="L26" s="59"/>
       <c r="M26" s="59"/>
@@ -4565,10 +4673,12 @@
       <c r="BJ26" s="59"/>
       <c r="BK26" s="59"/>
       <c r="BL26" s="59"/>
-    </row>
-    <row r="27" spans="1:64" s="38" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="BM26" s="59"/>
+      <c r="BN26" s="59"/>
+    </row>
+    <row r="27" spans="1:66" s="38" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A27" s="124" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B27" s="125" t="s">
         <v>19</v>
@@ -4586,10 +4696,10 @@
         <f>D27+E27</f>
         <v>46335</v>
       </c>
-      <c r="G27" s="9"/>
-      <c r="H27" s="5"/>
-      <c r="I27" s="59"/>
-      <c r="J27" s="59"/>
+      <c r="G27" s="128"/>
+      <c r="H27" s="128"/>
+      <c r="I27" s="9"/>
+      <c r="J27" s="5"/>
       <c r="K27" s="59"/>
       <c r="L27" s="59"/>
       <c r="M27" s="59"/>
@@ -4644,23 +4754,25 @@
       <c r="BJ27" s="59"/>
       <c r="BK27" s="59"/>
       <c r="BL27" s="59"/>
-    </row>
-    <row r="28" spans="1:64" s="38" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="BM27" s="59"/>
+      <c r="BN27" s="59"/>
+    </row>
+    <row r="28" spans="1:66" s="38" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" s="99" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B28" s="57"/>
       <c r="C28" s="58"/>
       <c r="D28" s="81"/>
       <c r="E28" s="94"/>
       <c r="F28" s="82"/>
-      <c r="G28" s="9"/>
-      <c r="H28" s="5" t="str">
+      <c r="G28" s="94"/>
+      <c r="H28" s="94"/>
+      <c r="I28" s="9"/>
+      <c r="J28" s="5" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="I28" s="59"/>
-      <c r="J28" s="59"/>
       <c r="K28" s="59"/>
       <c r="L28" s="59"/>
       <c r="M28" s="59"/>
@@ -4715,10 +4827,12 @@
       <c r="BJ28" s="59"/>
       <c r="BK28" s="59"/>
       <c r="BL28" s="59"/>
-    </row>
-    <row r="29" spans="1:64" s="38" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="BM28" s="59"/>
+      <c r="BN28" s="59"/>
+    </row>
+    <row r="29" spans="1:66" s="38" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A29" s="130" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B29" s="131" t="s">
         <v>15</v>
@@ -4736,13 +4850,17 @@
         <f>D29+E29</f>
         <v>46341</v>
       </c>
-      <c r="G29" s="9"/>
-      <c r="H29" s="5">
+      <c r="G29" s="134">
+        <v>4</v>
+      </c>
+      <c r="H29" s="134">
+        <v>1</v>
+      </c>
+      <c r="I29" s="9"/>
+      <c r="J29" s="5">
         <f t="shared" si="4"/>
-        <v>6</v>
-      </c>
-      <c r="I29" s="41"/>
-      <c r="J29" s="41"/>
+        <v>-46334</v>
+      </c>
       <c r="K29" s="41"/>
       <c r="L29" s="41"/>
       <c r="M29" s="41"/>
@@ -4797,10 +4915,12 @@
       <c r="BJ29" s="41"/>
       <c r="BK29" s="41"/>
       <c r="BL29" s="41"/>
-    </row>
-    <row r="30" spans="1:64" s="38" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="BM29" s="41"/>
+      <c r="BN29" s="41"/>
+    </row>
+    <row r="30" spans="1:66" s="38" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="137" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B30" s="138" t="s">
         <v>13</v>
@@ -4818,13 +4938,15 @@
         <f>D30+E30</f>
         <v>46341</v>
       </c>
-      <c r="G30" s="9"/>
-      <c r="H30" s="5">
+      <c r="G30" s="136">
+        <v>6</v>
+      </c>
+      <c r="H30" s="136"/>
+      <c r="I30" s="9"/>
+      <c r="J30" s="5" t="str">
         <f t="shared" si="4"/>
-        <v>6</v>
-      </c>
-      <c r="I30" s="41"/>
-      <c r="J30" s="41"/>
+        <v/>
+      </c>
       <c r="K30" s="41"/>
       <c r="L30" s="41"/>
       <c r="M30" s="41"/>
@@ -4879,10 +5001,12 @@
       <c r="BJ30" s="41"/>
       <c r="BK30" s="41"/>
       <c r="BL30" s="41"/>
-    </row>
-    <row r="31" spans="1:64" s="38" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="BM30" s="41"/>
+      <c r="BN30" s="41"/>
+    </row>
+    <row r="31" spans="1:66" s="38" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A31" s="157" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B31" s="158"/>
       <c r="C31" s="159"/>
@@ -4896,13 +5020,13 @@
         <f>D31+E31</f>
         <v>46342</v>
       </c>
-      <c r="G31" s="9"/>
-      <c r="H31" s="5">
+      <c r="G31" s="161"/>
+      <c r="H31" s="161"/>
+      <c r="I31" s="9"/>
+      <c r="J31" s="5" t="str">
         <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="I31" s="41"/>
-      <c r="J31" s="41"/>
+        <v/>
+      </c>
       <c r="K31" s="41"/>
       <c r="L31" s="41"/>
       <c r="M31" s="41"/>
@@ -4957,21 +5081,23 @@
       <c r="BJ31" s="41"/>
       <c r="BK31" s="41"/>
       <c r="BL31" s="41"/>
-    </row>
-    <row r="32" spans="1:64" s="38" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="BM31" s="41"/>
+      <c r="BN31" s="41"/>
+    </row>
+    <row r="32" spans="1:66" s="38" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="60"/>
       <c r="B32" s="61"/>
       <c r="C32" s="62"/>
       <c r="D32" s="63"/>
       <c r="E32" s="63"/>
       <c r="F32" s="63"/>
-      <c r="G32" s="9"/>
-      <c r="H32" s="5" t="str">
+      <c r="G32" s="63"/>
+      <c r="H32" s="63"/>
+      <c r="I32" s="9"/>
+      <c r="J32" s="5" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="I32" s="37"/>
-      <c r="J32" s="37"/>
       <c r="K32" s="37"/>
       <c r="L32" s="37"/>
       <c r="M32" s="37"/>
@@ -5026,21 +5152,23 @@
       <c r="BJ32" s="37"/>
       <c r="BK32" s="37"/>
       <c r="BL32" s="37"/>
-    </row>
-    <row r="33" spans="1:64" s="38" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="BM32" s="37"/>
+      <c r="BN32" s="37"/>
+    </row>
+    <row r="33" spans="1:66" s="38" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33" s="64"/>
       <c r="B33" s="65"/>
       <c r="C33" s="66"/>
       <c r="D33" s="67"/>
       <c r="E33" s="67"/>
-      <c r="F33" s="68"/>
-      <c r="G33" s="9"/>
-      <c r="H33" s="6" t="str">
+      <c r="F33" s="67"/>
+      <c r="G33" s="67"/>
+      <c r="H33" s="68"/>
+      <c r="I33" s="9"/>
+      <c r="J33" s="6" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="I33" s="69"/>
-      <c r="J33" s="69"/>
       <c r="K33" s="69"/>
       <c r="L33" s="69"/>
       <c r="M33" s="69"/>
@@ -5095,37 +5223,41 @@
       <c r="BJ33" s="69"/>
       <c r="BK33" s="69"/>
       <c r="BL33" s="69"/>
-    </row>
-    <row r="34" spans="1:64" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="G34" s="3"/>
-    </row>
-    <row r="35" spans="1:64" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="BM33" s="69"/>
+      <c r="BN33" s="69"/>
+    </row>
+    <row r="34" spans="1:66" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="I34" s="3"/>
+    </row>
+    <row r="35" spans="1:66" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B35" s="8"/>
-      <c r="F35" s="7"/>
-    </row>
-    <row r="36" spans="1:64" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H35" s="7"/>
+    </row>
+    <row r="36" spans="1:66" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B36" s="4"/>
     </row>
   </sheetData>
-  <mergeCells count="18">
-    <mergeCell ref="I1:O1"/>
-    <mergeCell ref="Q1:Z1"/>
-    <mergeCell ref="I2:O2"/>
-    <mergeCell ref="Q2:Z2"/>
-    <mergeCell ref="I4:O4"/>
-    <mergeCell ref="P4:V4"/>
-    <mergeCell ref="W4:AC4"/>
-    <mergeCell ref="AY4:BE4"/>
-    <mergeCell ref="BF4:BL4"/>
+  <mergeCells count="20">
+    <mergeCell ref="BA4:BG4"/>
+    <mergeCell ref="BH4:BN4"/>
     <mergeCell ref="A5:A6"/>
     <mergeCell ref="B5:B6"/>
     <mergeCell ref="C5:C6"/>
     <mergeCell ref="D5:D6"/>
     <mergeCell ref="E5:E6"/>
     <mergeCell ref="F5:F6"/>
-    <mergeCell ref="AD4:AJ4"/>
-    <mergeCell ref="AK4:AQ4"/>
-    <mergeCell ref="AR4:AX4"/>
+    <mergeCell ref="AF4:AL4"/>
+    <mergeCell ref="AM4:AS4"/>
+    <mergeCell ref="AT4:AZ4"/>
+    <mergeCell ref="G5:G6"/>
+    <mergeCell ref="H5:H6"/>
+    <mergeCell ref="K1:Q1"/>
+    <mergeCell ref="S1:AB1"/>
+    <mergeCell ref="K2:Q2"/>
+    <mergeCell ref="S2:AB2"/>
+    <mergeCell ref="K4:Q4"/>
+    <mergeCell ref="R4:X4"/>
+    <mergeCell ref="Y4:AE4"/>
   </mergeCells>
   <conditionalFormatting sqref="C7:C33">
     <cfRule type="dataBar" priority="8">
@@ -5141,45 +5273,45 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I4:BL19 I20:AC20 AE20:BL20 I21:BL31">
+  <conditionalFormatting sqref="K4:BN19 K20:AE20 AG20:BN20 K21:BN31">
     <cfRule type="expression" dxfId="8" priority="1">
-      <formula>AND(TODAY()&gt;=I$5, TODAY()&lt;J$5)</formula>
+      <formula>AND(TODAY()&gt;=K$5, TODAY()&lt;L$5)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I9:BL10">
+  <conditionalFormatting sqref="K9:BN10">
     <cfRule type="expression" dxfId="7" priority="6">
-      <formula>AND(task_start&lt;=I$5,ROUNDDOWN((task_end-task_start+1)*task_progress,0)+task_start-1&gt;=I$5)</formula>
+      <formula>AND(task_start&lt;=K$5,ROUNDDOWN((task_end-task_start+1)*task_progress,0)+task_start-1&gt;=K$5)</formula>
     </cfRule>
     <cfRule type="expression" dxfId="6" priority="7" stopIfTrue="1">
-      <formula>AND(task_end&gt;=I$5,task_start&lt;J$5)</formula>
+      <formula>AND(task_end&gt;=K$5,task_start&lt;L$5)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I12:BL14">
+  <conditionalFormatting sqref="K12:BN14">
     <cfRule type="expression" dxfId="5" priority="4">
-      <formula>AND(task_start&lt;=I$5,ROUNDDOWN((task_end-task_start+1)*task_progress,0)+task_start-1&gt;=I$5)</formula>
+      <formula>AND(task_start&lt;=K$5,ROUNDDOWN((task_end-task_start+1)*task_progress,0)+task_start-1&gt;=K$5)</formula>
     </cfRule>
     <cfRule type="expression" dxfId="4" priority="5" stopIfTrue="1">
-      <formula>AND(task_end&gt;=I$5,task_start&lt;J$5)</formula>
+      <formula>AND(task_end&gt;=K$5,task_start&lt;L$5)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I16:BL19 I20:AC20 AE20:BL20 I21:BL27">
+  <conditionalFormatting sqref="K16:BN19 K20:AE20 AG20:BN20 K21:BN27">
     <cfRule type="expression" dxfId="3" priority="2">
-      <formula>AND(task_start&lt;=I$5,ROUNDDOWN((task_end-task_start+1)*task_progress,0)+task_start-1&gt;=I$5)</formula>
+      <formula>AND(task_start&lt;=K$5,ROUNDDOWN((task_end-task_start+1)*task_progress,0)+task_start-1&gt;=K$5)</formula>
     </cfRule>
     <cfRule type="expression" dxfId="2" priority="3" stopIfTrue="1">
-      <formula>AND(task_end&gt;=I$5,task_start&lt;J$5)</formula>
+      <formula>AND(task_end&gt;=K$5,task_start&lt;L$5)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I29:BL31">
+  <conditionalFormatting sqref="K29:BN31">
     <cfRule type="expression" dxfId="1" priority="9">
-      <formula>AND(task_start&lt;=I$5,ROUNDDOWN((task_end-task_start+1)*task_progress,0)+task_start-1&gt;=I$5)</formula>
+      <formula>AND(task_start&lt;=K$5,ROUNDDOWN((task_end-task_start+1)*task_progress,0)+task_start-1&gt;=K$5)</formula>
     </cfRule>
     <cfRule type="expression" dxfId="0" priority="10" stopIfTrue="1">
-      <formula>AND(task_end&gt;=I$5,task_start&lt;J$5)</formula>
+      <formula>AND(task_end&gt;=K$5,task_start&lt;L$5)</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="1">
-    <dataValidation type="whole" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" promptTitle="Display Week" prompt="Changing this number will scroll the Gantt Chart view." sqref="Q2" xr:uid="{5055D4DC-4AC9-4908-8988-4E07AB8DE9B0}">
+  <dataValidations disablePrompts="1" count="1">
+    <dataValidation type="whole" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" promptTitle="Display Week" prompt="Changing this number will scroll the Gantt Chart view." sqref="S2" xr:uid="{5055D4DC-4AC9-4908-8988-4E07AB8DE9B0}">
       <formula1>1</formula1>
     </dataValidation>
   </dataValidations>
@@ -5228,27 +5360,27 @@
   <sheetData>
     <row r="2" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B2" s="170" t="s">
+        <v>36</v>
+      </c>
+      <c r="C2" s="150" t="s">
+        <v>37</v>
+      </c>
+      <c r="D2" s="150" t="s">
         <v>38</v>
       </c>
-      <c r="C2" s="150" t="s">
+      <c r="E2" s="150" t="s">
         <v>39</v>
       </c>
-      <c r="D2" s="150" t="s">
+      <c r="F2" s="150" t="s">
         <v>40</v>
       </c>
-      <c r="E2" s="150" t="s">
+    </row>
+    <row r="3" spans="2:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="191" t="s">
         <v>41</v>
       </c>
-      <c r="F2" s="150" t="s">
+      <c r="C3" s="151" t="s">
         <v>42</v>
-      </c>
-    </row>
-    <row r="3" spans="2:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="186" t="s">
-        <v>43</v>
-      </c>
-      <c r="C3" s="151" t="s">
-        <v>44</v>
       </c>
       <c r="D3" s="149"/>
       <c r="E3" s="149"/>
@@ -5258,9 +5390,9 @@
       </c>
     </row>
     <row r="4" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B4" s="186"/>
+      <c r="B4" s="191"/>
       <c r="C4" s="149" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D4" s="149"/>
       <c r="E4" s="149"/>
@@ -5270,9 +5402,9 @@
       </c>
     </row>
     <row r="5" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B5" s="186"/>
+      <c r="B5" s="191"/>
       <c r="C5" s="149" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D5" s="149"/>
       <c r="E5" s="149"/>
@@ -5282,9 +5414,9 @@
       </c>
     </row>
     <row r="6" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B6" s="186"/>
+      <c r="B6" s="191"/>
       <c r="C6" s="149" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D6" s="149"/>
       <c r="E6" s="149"/>
@@ -5294,7 +5426,7 @@
       </c>
     </row>
     <row r="7" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B7" s="186"/>
+      <c r="B7" s="191"/>
       <c r="C7" s="149"/>
       <c r="D7" s="149"/>
       <c r="E7" s="149"/>
@@ -5304,7 +5436,7 @@
       </c>
     </row>
     <row r="8" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B8" s="186"/>
+      <c r="B8" s="191"/>
       <c r="C8" s="149"/>
       <c r="D8" s="149"/>
       <c r="E8" s="149"/>
@@ -5314,7 +5446,7 @@
       </c>
     </row>
     <row r="9" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B9" s="186"/>
+      <c r="B9" s="191"/>
       <c r="C9" s="149"/>
       <c r="D9" s="149"/>
       <c r="E9" s="149"/>
@@ -5324,7 +5456,7 @@
       </c>
     </row>
     <row r="10" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B10" s="186"/>
+      <c r="B10" s="191"/>
       <c r="C10" s="149"/>
       <c r="D10" s="149"/>
       <c r="E10" s="149"/>
@@ -5334,7 +5466,7 @@
       </c>
     </row>
     <row r="11" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B11" s="186"/>
+      <c r="B11" s="191"/>
       <c r="C11" s="149"/>
       <c r="D11" s="149"/>
       <c r="E11" s="149"/>
@@ -5344,7 +5476,7 @@
       </c>
     </row>
     <row r="12" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B12" s="186"/>
+      <c r="B12" s="191"/>
       <c r="C12" s="149"/>
       <c r="D12" s="149"/>
       <c r="E12" s="149"/>
@@ -5354,8 +5486,8 @@
       </c>
     </row>
     <row r="13" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B13" s="186" t="s">
-        <v>48</v>
+      <c r="B13" s="191" t="s">
+        <v>46</v>
       </c>
       <c r="C13" s="149"/>
       <c r="D13" s="149"/>
@@ -5366,7 +5498,7 @@
       </c>
     </row>
     <row r="14" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B14" s="186"/>
+      <c r="B14" s="191"/>
       <c r="C14" s="149"/>
       <c r="D14" s="149"/>
       <c r="E14" s="149"/>
@@ -5376,7 +5508,7 @@
       </c>
     </row>
     <row r="15" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B15" s="186"/>
+      <c r="B15" s="191"/>
       <c r="C15" s="149"/>
       <c r="D15" s="149"/>
       <c r="E15" s="149"/>
@@ -5386,7 +5518,7 @@
       </c>
     </row>
     <row r="16" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B16" s="186"/>
+      <c r="B16" s="191"/>
       <c r="C16" s="149"/>
       <c r="D16" s="149"/>
       <c r="E16" s="149"/>
@@ -5396,7 +5528,7 @@
       </c>
     </row>
     <row r="17" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B17" s="186"/>
+      <c r="B17" s="191"/>
       <c r="C17" s="149"/>
       <c r="D17" s="149"/>
       <c r="E17" s="149"/>
@@ -5406,7 +5538,7 @@
       </c>
     </row>
     <row r="18" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B18" s="186"/>
+      <c r="B18" s="191"/>
       <c r="C18" s="149"/>
       <c r="D18" s="149"/>
       <c r="E18" s="149"/>
@@ -5416,7 +5548,7 @@
       </c>
     </row>
     <row r="19" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B19" s="186"/>
+      <c r="B19" s="191"/>
       <c r="C19" s="149"/>
       <c r="D19" s="149"/>
       <c r="E19" s="149"/>
@@ -5426,7 +5558,7 @@
       </c>
     </row>
     <row r="20" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B20" s="186"/>
+      <c r="B20" s="191"/>
       <c r="C20" s="149"/>
       <c r="D20" s="149"/>
       <c r="E20" s="149"/>
@@ -5436,7 +5568,7 @@
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B21" s="186"/>
+      <c r="B21" s="191"/>
       <c r="C21" s="149"/>
       <c r="D21" s="149"/>
       <c r="E21" s="149"/>
@@ -5446,7 +5578,7 @@
       </c>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B22" s="186"/>
+      <c r="B22" s="191"/>
       <c r="C22" s="149"/>
       <c r="D22" s="149"/>
       <c r="E22" s="149"/>
@@ -5456,7 +5588,7 @@
       </c>
     </row>
     <row r="23" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B23" s="186"/>
+      <c r="B23" s="191"/>
       <c r="C23" s="149"/>
       <c r="D23" s="149"/>
       <c r="E23" s="149"/>
@@ -5491,47 +5623,47 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B1" s="187" t="s">
-        <v>49</v>
-      </c>
-      <c r="C1" s="188"/>
-      <c r="D1" s="188"/>
-      <c r="E1" s="188"/>
-      <c r="F1" s="188"/>
-      <c r="G1" s="189"/>
+      <c r="B1" s="173" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1" s="174"/>
+      <c r="D1" s="174"/>
+      <c r="E1" s="174"/>
+      <c r="F1" s="174"/>
+      <c r="G1" s="175"/>
     </row>
     <row r="2" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D2" t="s">
         <v>50</v>
       </c>
-      <c r="C2" t="s">
+      <c r="E2" t="s">
         <v>51</v>
       </c>
-      <c r="D2" t="s">
+      <c r="F2" t="s">
         <v>52</v>
       </c>
-      <c r="E2" t="s">
+      <c r="G2" t="s">
         <v>53</v>
-      </c>
-      <c r="F2" t="s">
-        <v>54</v>
-      </c>
-      <c r="G2" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="3" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B3" s="145" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C3" s="145" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D3">
         <v>1</v>
       </c>
       <c r="E3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F3" s="144">
         <v>13000</v>
@@ -5543,16 +5675,16 @@
     </row>
     <row r="4" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B4" s="145" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C4" s="145" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D4">
         <v>1</v>
       </c>
       <c r="E4" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F4" s="144">
         <v>13000</v>
@@ -5563,16 +5695,16 @@
     </row>
     <row r="5" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B5" s="145" t="s">
-        <v>90</v>
-      </c>
-      <c r="C5" s="191" t="s">
-        <v>59</v>
+        <v>88</v>
+      </c>
+      <c r="C5" s="172" t="s">
+        <v>57</v>
       </c>
       <c r="D5">
         <v>2</v>
       </c>
       <c r="E5" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F5" s="144">
         <v>40000</v>
@@ -5584,16 +5716,16 @@
     </row>
     <row r="6" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B6" s="145" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C6" s="145" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D6">
         <v>1</v>
       </c>
       <c r="E6" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F6" s="144">
         <v>5000</v>
@@ -5604,16 +5736,16 @@
     </row>
     <row r="7" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B7" s="145" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C7" s="145" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D7">
         <v>2</v>
       </c>
       <c r="E7" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F7" s="144">
         <v>5500</v>
@@ -5625,16 +5757,16 @@
     </row>
     <row r="8" spans="2:17" ht="28" x14ac:dyDescent="0.3">
       <c r="B8" s="145" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C8" s="145" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D8">
         <v>1</v>
       </c>
       <c r="E8" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F8" s="144">
         <v>6000</v>
@@ -5646,16 +5778,16 @@
     </row>
     <row r="9" spans="2:17" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B9" s="145" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C9" s="145" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D9">
         <v>2</v>
       </c>
       <c r="E9" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F9" s="144">
         <v>3000</v>
@@ -5667,16 +5799,16 @@
     </row>
     <row r="10" spans="2:17" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B10" s="145" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C10" s="145" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D10">
         <v>1</v>
       </c>
       <c r="E10" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F10" s="144">
         <v>13000</v>
@@ -5685,25 +5817,25 @@
         <f>Tabla1[[#This Row],[Precio unitario]]*Tabla1[[#This Row],[Cantidad]]</f>
         <v>13000</v>
       </c>
-      <c r="L10" s="187"/>
-      <c r="M10" s="188"/>
-      <c r="N10" s="188"/>
-      <c r="O10" s="188"/>
-      <c r="P10" s="188"/>
-      <c r="Q10" s="189"/>
+      <c r="L10" s="173"/>
+      <c r="M10" s="174"/>
+      <c r="N10" s="174"/>
+      <c r="O10" s="174"/>
+      <c r="P10" s="174"/>
+      <c r="Q10" s="175"/>
     </row>
     <row r="11" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B11" s="145" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C11" s="145" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D11">
         <v>1</v>
       </c>
       <c r="E11" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F11" s="144">
         <v>6000</v>
@@ -5715,16 +5847,16 @@
     </row>
     <row r="12" spans="2:17" ht="28" x14ac:dyDescent="0.3">
       <c r="B12" s="145" t="s">
-        <v>67</v>
-      </c>
-      <c r="C12" s="190" t="s">
-        <v>66</v>
+        <v>65</v>
+      </c>
+      <c r="C12" s="171" t="s">
+        <v>64</v>
       </c>
       <c r="D12">
         <v>3</v>
       </c>
       <c r="E12" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F12" s="144">
         <v>11000</v>
@@ -5740,16 +5872,16 @@
     </row>
     <row r="13" spans="2:17" ht="28" x14ac:dyDescent="0.3">
       <c r="B13" s="145" t="s">
-        <v>69</v>
-      </c>
-      <c r="C13" s="191" t="s">
-        <v>68</v>
+        <v>67</v>
+      </c>
+      <c r="C13" s="172" t="s">
+        <v>66</v>
       </c>
       <c r="D13">
         <v>1</v>
       </c>
       <c r="E13" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F13" s="144">
         <v>5000</v>
@@ -5765,16 +5897,16 @@
     </row>
     <row r="14" spans="2:17" ht="28" x14ac:dyDescent="0.3">
       <c r="B14" s="145" t="s">
-        <v>71</v>
-      </c>
-      <c r="C14" s="190" t="s">
-        <v>70</v>
+        <v>69</v>
+      </c>
+      <c r="C14" s="171" t="s">
+        <v>68</v>
       </c>
       <c r="D14">
         <v>1</v>
       </c>
       <c r="E14" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F14" s="144">
         <v>5000</v>
@@ -5790,16 +5922,16 @@
     </row>
     <row r="15" spans="2:17" ht="28" x14ac:dyDescent="0.3">
       <c r="B15" s="145" t="s">
-        <v>73</v>
-      </c>
-      <c r="C15" s="191" t="s">
-        <v>72</v>
+        <v>71</v>
+      </c>
+      <c r="C15" s="172" t="s">
+        <v>70</v>
       </c>
       <c r="D15">
         <v>3</v>
       </c>
       <c r="E15" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F15" s="144">
         <v>2300</v>
@@ -5815,16 +5947,16 @@
     </row>
     <row r="16" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B16" s="145" t="s">
-        <v>75</v>
-      </c>
-      <c r="C16" s="190" t="s">
-        <v>74</v>
+        <v>73</v>
+      </c>
+      <c r="C16" s="171" t="s">
+        <v>72</v>
       </c>
       <c r="D16">
         <v>1</v>
       </c>
       <c r="E16" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F16" s="144">
         <v>5000</v>
@@ -5840,16 +5972,16 @@
     </row>
     <row r="17" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B17" s="145" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C17" s="145" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D17">
         <v>5</v>
       </c>
       <c r="E17" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F17" s="144">
         <v>2000</v>
@@ -5865,16 +5997,16 @@
     </row>
     <row r="18" spans="2:17" ht="28" x14ac:dyDescent="0.3">
       <c r="B18" s="145" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C18" s="145" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D18">
         <v>1</v>
       </c>
       <c r="E18" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F18" s="144">
         <v>3000</v>
@@ -5890,16 +6022,16 @@
     </row>
     <row r="19" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B19" s="145" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C19" s="145" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D19">
         <v>1</v>
       </c>
       <c r="E19" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F19" s="144">
         <v>15000</v>
@@ -5915,16 +6047,16 @@
     </row>
     <row r="20" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B20" s="145" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C20" s="145" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D20">
         <v>1</v>
       </c>
       <c r="E20" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F20" s="144">
         <v>40000</v>
@@ -5940,16 +6072,16 @@
     </row>
     <row r="21" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B21" s="145" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C21" s="145" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D21">
         <v>40</v>
       </c>
       <c r="E21" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F21" s="144">
         <v>7000</v>
@@ -5964,11 +6096,11 @@
     </row>
     <row r="22" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B22" s="145" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C22" s="145"/>
       <c r="E22" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F22" s="144"/>
       <c r="G22" s="144"/>
@@ -5979,13 +6111,13 @@
     </row>
     <row r="23" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B23" s="145" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C23" s="145" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E23" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F23" s="144"/>
       <c r="G23" s="144"/>
@@ -5996,10 +6128,10 @@
     </row>
     <row r="24" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B24" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F24" s="146" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="G24" s="144">
         <f>SUBTOTAL(109,Tabla1[Total])</f>
@@ -6012,7 +6144,7 @@
     </row>
     <row r="25" spans="2:17" x14ac:dyDescent="0.3">
       <c r="F25" s="147" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="G25" s="148">
         <f>Tabla1[[#Totals],[Total]]/1570</f>
@@ -6075,35 +6207,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <Image xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
-      <Url xsi:nil="true"/>
-      <Description xsi:nil="true"/>
-    </Image>
-    <Status xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">Not started</Status>
-    <Background xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">false</Background>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <ImageTagsTaxHTField xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </ImageTagsTaxHTField>
-    <TaxCatchAll xmlns="230e9df3-be65-4c73-a93b-d1236ebd677e" xsi:nil="true"/>
-    <MediaServiceKeyPoints xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010079F111ED35F8CC479449609E8A0923A6" ma:contentTypeVersion="28" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="60f5a4f2d2b0abadcf532d48ebf9cb71">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xmlns:ns3="16c05727-aa75-4e4a-9b5f-8a80a1165891" xmlns:ns4="230e9df3-be65-4c73-a93b-d1236ebd677e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="7dd78129e6a1811f84807ad11c651531" ns1:_="" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -6415,27 +6518,36 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A82239A0-E68C-493F-BEE6-C77FEA397FD6}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5"/>
-    <ds:schemaRef ds:uri="230e9df3-be65-4c73-a93b-d1236ebd677e"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97245281-08F3-4104-84BD-39F3D8CFB195}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <Image xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
+      <Url xsi:nil="true"/>
+      <Description xsi:nil="true"/>
+    </Image>
+    <Status xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">Not started</Status>
+    <Background xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">false</Background>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <ImageTagsTaxHTField xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </ImageTagsTaxHTField>
+    <TaxCatchAll xmlns="230e9df3-be65-4c73-a93b-d1236ebd677e" xsi:nil="true"/>
+    <MediaServiceKeyPoints xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A09426A3-87E9-4865-8A6C-3456B026AE03}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -6456,6 +6568,26 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97245281-08F3-4104-84BD-39F3D8CFB195}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A82239A0-E68C-493F-BEE6-C77FEA397FD6}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5"/>
+    <ds:schemaRef ds:uri="230e9df3-be65-4c73-a93b-d1236ebd677e"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata"/>
 </file>
--- a/Informes/Gantt Vehículo Autónomo.xlsx
+++ b/Informes/Gantt Vehículo Autónomo.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a31f0271d0b8797b/Desktop/Proyecto Ingenieria/INFORMES/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a31f0271d0b8797b/Desktop/Proyecto Ingenieria/2026_2C_PF_VEHICULO-AUTONOMO-MARCADO-DE-LAYOUTS_ESPINOLA-SULLCA-main/Informes/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="646" documentId="8_{A2B61D2F-08BD-40F5-ACC5-C73775A42AA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9ABC49D0-F1D8-47A4-B507-E0F67FD6380F}"/>
+  <xr:revisionPtr revIDLastSave="654" documentId="8_{A2B61D2F-08BD-40F5-ACC5-C73775A42AA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B6F830BB-8838-4375-B993-848ABF3B6A14}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1692,14 +1692,39 @@
     <xf numFmtId="0" fontId="0" fillId="20" borderId="40" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="15" fillId="17" borderId="21" xfId="10" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="19" borderId="21" xfId="10" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="15" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="15" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="11" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="11" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="11" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="11" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="11" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="11" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="8" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1716,42 +1741,17 @@
     <xf numFmtId="167" fontId="15" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="15" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="15" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="11" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="11" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="11" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="11" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="18" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="17" borderId="21" xfId="10" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="19" borderId="21" xfId="10" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="11" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="11" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="14">
@@ -1894,6 +1894,25 @@
       </border>
     </dxf>
     <dxf>
+      <numFmt numFmtId="169" formatCode="_-[$$-409]* #,##0_ ;_-[$$-409]* \-#,##0\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="169" formatCode="_-[$$-409]* #,##0_ ;_-[$$-409]* \-#,##0\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="169" formatCode="_-[$$-409]* #,##0_ ;_-[$$-409]* \-#,##0\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="169" formatCode="_-[$$-409]* #,##0_ ;_-[$$-409]* \-#,##0\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
@@ -1990,25 +2009,6 @@
         <top/>
         <bottom/>
       </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="169" formatCode="_-[$$-409]* #,##0_ ;_-[$$-409]* \-#,##0\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="169" formatCode="_-[$$-409]* #,##0_ ;_-[$$-409]* \-#,##0\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="169" formatCode="_-[$$-409]* #,##0_ ;_-[$$-409]* \-#,##0\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="169" formatCode="_-[$$-409]* #,##0_ ;_-[$$-409]* \-#,##0\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <border>
@@ -2208,7 +2208,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{7B046895-9170-4AC6-8C65-BF0F2537217B}" name="Tabla3" displayName="Tabla3" ref="C2:F23" totalsRowShown="0" headerRowDxfId="13">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{7B046895-9170-4AC6-8C65-BF0F2537217B}" name="Tabla3" displayName="Tabla3" ref="C2:F23" totalsRowShown="0" headerRowDxfId="19">
   <autoFilter ref="C2:F23" xr:uid="{7B046895-9170-4AC6-8C65-BF0F2537217B}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -2216,10 +2216,10 @@
     <filterColumn colId="3" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{677FC96E-7F25-4A06-87E3-922FDD41B915}" name="Tarea" dataDxfId="12"/>
-    <tableColumn id="2" xr3:uid="{58277187-363E-428B-A83B-BC14DB987A6B}" name="Horas estimadas" dataDxfId="11"/>
-    <tableColumn id="3" xr3:uid="{488EC91C-90C1-4FC4-A305-62832539CD69}" name="Horas reales" dataDxfId="10"/>
-    <tableColumn id="4" xr3:uid="{C0DE1A19-3FEF-4849-899B-C98251D2724D}" name="Diferencia" dataDxfId="9">
+    <tableColumn id="1" xr3:uid="{677FC96E-7F25-4A06-87E3-922FDD41B915}" name="Tarea" dataDxfId="18"/>
+    <tableColumn id="2" xr3:uid="{58277187-363E-428B-A83B-BC14DB987A6B}" name="Horas estimadas" dataDxfId="17"/>
+    <tableColumn id="3" xr3:uid="{488EC91C-90C1-4FC4-A305-62832539CD69}" name="Horas reales" dataDxfId="16"/>
+    <tableColumn id="4" xr3:uid="{C0DE1A19-3FEF-4849-899B-C98251D2724D}" name="Diferencia" dataDxfId="15">
       <calculatedColumnFormula>Tabla3[[#This Row],[Horas reales]]-Tabla3[[#This Row],[Horas estimadas]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -2238,12 +2238,12 @@
     <filterColumn colId="5" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{45ACA5F6-477D-42B6-B421-4AEE018B4E81}" name="Nombre" totalsRowLabel="Total" dataDxfId="19"/>
-    <tableColumn id="2" xr3:uid="{CDC2B791-5EFB-4C87-AAD3-192DBB5C19D6}" name="Descripción" dataDxfId="18"/>
+    <tableColumn id="1" xr3:uid="{45ACA5F6-477D-42B6-B421-4AEE018B4E81}" name="Nombre" totalsRowLabel="Total" dataDxfId="14"/>
+    <tableColumn id="2" xr3:uid="{CDC2B791-5EFB-4C87-AAD3-192DBB5C19D6}" name="Descripción" dataDxfId="13"/>
     <tableColumn id="3" xr3:uid="{95A5BD7C-444C-4C6D-BE74-E16B3FFFEE8E}" name="Cantidad"/>
     <tableColumn id="4" xr3:uid="{FF7F68A1-0DEA-4B69-8384-B1FE22AD9958}" name="Proveedor"/>
-    <tableColumn id="5" xr3:uid="{63F8E491-A0B5-4A72-A3FF-8221530F268B}" name="Precio unitario" totalsRowLabel=" $ARS " dataDxfId="17" totalsRowDxfId="16"/>
-    <tableColumn id="6" xr3:uid="{1E275AE4-1059-4BEF-B3F7-9BB27037631B}" name="Total" totalsRowFunction="sum" dataDxfId="15" totalsRowDxfId="14"/>
+    <tableColumn id="5" xr3:uid="{63F8E491-A0B5-4A72-A3FF-8221530F268B}" name="Precio unitario" totalsRowLabel=" $ARS " dataDxfId="12" totalsRowDxfId="11"/>
+    <tableColumn id="6" xr3:uid="{1E275AE4-1059-4BEF-B3F7-9BB27037631B}" name="Total" totalsRowFunction="sum" dataDxfId="10" totalsRowDxfId="9"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium4" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2499,28 +2499,28 @@
       <c r="G1" s="12"/>
       <c r="H1" s="13"/>
       <c r="J1" s="1"/>
-      <c r="K1" s="176" t="s">
+      <c r="K1" s="185" t="s">
         <v>1</v>
       </c>
-      <c r="L1" s="177"/>
-      <c r="M1" s="177"/>
-      <c r="N1" s="177"/>
-      <c r="O1" s="177"/>
-      <c r="P1" s="177"/>
-      <c r="Q1" s="177"/>
+      <c r="L1" s="186"/>
+      <c r="M1" s="186"/>
+      <c r="N1" s="186"/>
+      <c r="O1" s="186"/>
+      <c r="P1" s="186"/>
+      <c r="Q1" s="186"/>
       <c r="R1" s="16"/>
-      <c r="S1" s="178">
+      <c r="S1" s="187">
         <v>46244</v>
       </c>
-      <c r="T1" s="179"/>
-      <c r="U1" s="179"/>
-      <c r="V1" s="179"/>
-      <c r="W1" s="179"/>
-      <c r="X1" s="179"/>
-      <c r="Y1" s="179"/>
-      <c r="Z1" s="179"/>
-      <c r="AA1" s="179"/>
-      <c r="AB1" s="179"/>
+      <c r="T1" s="188"/>
+      <c r="U1" s="188"/>
+      <c r="V1" s="188"/>
+      <c r="W1" s="188"/>
+      <c r="X1" s="188"/>
+      <c r="Y1" s="188"/>
+      <c r="Z1" s="188"/>
+      <c r="AA1" s="188"/>
+      <c r="AB1" s="188"/>
     </row>
     <row r="2" spans="1:66" ht="30" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A2" s="71" t="s">
@@ -2535,28 +2535,28 @@
       <c r="F2" s="15"/>
       <c r="G2" s="15"/>
       <c r="H2" s="14"/>
-      <c r="K2" s="176" t="s">
+      <c r="K2" s="185" t="s">
         <v>4</v>
       </c>
-      <c r="L2" s="177"/>
-      <c r="M2" s="177"/>
-      <c r="N2" s="177"/>
-      <c r="O2" s="177"/>
-      <c r="P2" s="177"/>
-      <c r="Q2" s="177"/>
+      <c r="L2" s="186"/>
+      <c r="M2" s="186"/>
+      <c r="N2" s="186"/>
+      <c r="O2" s="186"/>
+      <c r="P2" s="186"/>
+      <c r="Q2" s="186"/>
       <c r="R2" s="16"/>
-      <c r="S2" s="180">
-        <v>2</v>
-      </c>
-      <c r="T2" s="181"/>
-      <c r="U2" s="181"/>
-      <c r="V2" s="181"/>
-      <c r="W2" s="181"/>
-      <c r="X2" s="181"/>
-      <c r="Y2" s="181"/>
-      <c r="Z2" s="181"/>
-      <c r="AA2" s="181"/>
-      <c r="AB2" s="181"/>
+      <c r="S2" s="189">
+        <v>1</v>
+      </c>
+      <c r="T2" s="190"/>
+      <c r="U2" s="190"/>
+      <c r="V2" s="190"/>
+      <c r="W2" s="190"/>
+      <c r="X2" s="190"/>
+      <c r="Y2" s="190"/>
+      <c r="Z2" s="190"/>
+      <c r="AA2" s="190"/>
+      <c r="AB2" s="190"/>
     </row>
     <row r="3" spans="1:66" s="18" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="17"/>
@@ -2572,346 +2572,346 @@
       <c r="E4" s="22"/>
       <c r="F4" s="22"/>
       <c r="G4" s="22"/>
-      <c r="K4" s="182">
+      <c r="K4" s="191">
         <f>K5</f>
+        <v>46244</v>
+      </c>
+      <c r="L4" s="175"/>
+      <c r="M4" s="175"/>
+      <c r="N4" s="175"/>
+      <c r="O4" s="175"/>
+      <c r="P4" s="175"/>
+      <c r="Q4" s="175"/>
+      <c r="R4" s="175">
+        <f>R5</f>
         <v>46251</v>
       </c>
-      <c r="L4" s="183"/>
-      <c r="M4" s="183"/>
-      <c r="N4" s="183"/>
-      <c r="O4" s="183"/>
-      <c r="P4" s="183"/>
-      <c r="Q4" s="183"/>
-      <c r="R4" s="183">
-        <f>R5</f>
+      <c r="S4" s="175"/>
+      <c r="T4" s="175"/>
+      <c r="U4" s="175"/>
+      <c r="V4" s="175"/>
+      <c r="W4" s="175"/>
+      <c r="X4" s="175"/>
+      <c r="Y4" s="175">
+        <f>Y5</f>
         <v>46258</v>
       </c>
-      <c r="S4" s="183"/>
-      <c r="T4" s="183"/>
-      <c r="U4" s="183"/>
-      <c r="V4" s="183"/>
-      <c r="W4" s="183"/>
-      <c r="X4" s="183"/>
-      <c r="Y4" s="183">
-        <f>Y5</f>
+      <c r="Z4" s="175"/>
+      <c r="AA4" s="175"/>
+      <c r="AB4" s="175"/>
+      <c r="AC4" s="175"/>
+      <c r="AD4" s="175"/>
+      <c r="AE4" s="175"/>
+      <c r="AF4" s="175">
+        <f>AF5</f>
         <v>46265</v>
       </c>
-      <c r="Z4" s="183"/>
-      <c r="AA4" s="183"/>
-      <c r="AB4" s="183"/>
-      <c r="AC4" s="183"/>
-      <c r="AD4" s="183"/>
-      <c r="AE4" s="183"/>
-      <c r="AF4" s="183">
-        <f>AF5</f>
+      <c r="AG4" s="175"/>
+      <c r="AH4" s="175"/>
+      <c r="AI4" s="175"/>
+      <c r="AJ4" s="175"/>
+      <c r="AK4" s="175"/>
+      <c r="AL4" s="175"/>
+      <c r="AM4" s="175">
+        <f>AM5</f>
         <v>46272</v>
       </c>
-      <c r="AG4" s="183"/>
-      <c r="AH4" s="183"/>
-      <c r="AI4" s="183"/>
-      <c r="AJ4" s="183"/>
-      <c r="AK4" s="183"/>
-      <c r="AL4" s="183"/>
-      <c r="AM4" s="183">
-        <f>AM5</f>
+      <c r="AN4" s="175"/>
+      <c r="AO4" s="175"/>
+      <c r="AP4" s="175"/>
+      <c r="AQ4" s="175"/>
+      <c r="AR4" s="175"/>
+      <c r="AS4" s="175"/>
+      <c r="AT4" s="175">
+        <f>AT5</f>
         <v>46279</v>
       </c>
-      <c r="AN4" s="183"/>
-      <c r="AO4" s="183"/>
-      <c r="AP4" s="183"/>
-      <c r="AQ4" s="183"/>
-      <c r="AR4" s="183"/>
-      <c r="AS4" s="183"/>
-      <c r="AT4" s="183">
-        <f>AT5</f>
+      <c r="AU4" s="175"/>
+      <c r="AV4" s="175"/>
+      <c r="AW4" s="175"/>
+      <c r="AX4" s="175"/>
+      <c r="AY4" s="175"/>
+      <c r="AZ4" s="175"/>
+      <c r="BA4" s="175">
+        <f>BA5</f>
         <v>46286</v>
       </c>
-      <c r="AU4" s="183"/>
-      <c r="AV4" s="183"/>
-      <c r="AW4" s="183"/>
-      <c r="AX4" s="183"/>
-      <c r="AY4" s="183"/>
-      <c r="AZ4" s="183"/>
-      <c r="BA4" s="183">
-        <f>BA5</f>
+      <c r="BB4" s="175"/>
+      <c r="BC4" s="175"/>
+      <c r="BD4" s="175"/>
+      <c r="BE4" s="175"/>
+      <c r="BF4" s="175"/>
+      <c r="BG4" s="175"/>
+      <c r="BH4" s="175">
+        <f>BH5</f>
         <v>46293</v>
       </c>
-      <c r="BB4" s="183"/>
-      <c r="BC4" s="183"/>
-      <c r="BD4" s="183"/>
-      <c r="BE4" s="183"/>
-      <c r="BF4" s="183"/>
-      <c r="BG4" s="183"/>
-      <c r="BH4" s="183">
-        <f>BH5</f>
-        <v>46300</v>
-      </c>
-      <c r="BI4" s="183"/>
-      <c r="BJ4" s="183"/>
-      <c r="BK4" s="183"/>
-      <c r="BL4" s="183"/>
-      <c r="BM4" s="183"/>
-      <c r="BN4" s="184"/>
+      <c r="BI4" s="175"/>
+      <c r="BJ4" s="175"/>
+      <c r="BK4" s="175"/>
+      <c r="BL4" s="175"/>
+      <c r="BM4" s="175"/>
+      <c r="BN4" s="176"/>
     </row>
     <row r="5" spans="1:66" s="18" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="185" t="s">
+      <c r="A5" s="177" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="187" t="s">
+      <c r="B5" s="179" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="189" t="s">
+      <c r="C5" s="181" t="s">
         <v>7</v>
       </c>
-      <c r="D5" s="189" t="s">
+      <c r="D5" s="181" t="s">
         <v>8</v>
       </c>
-      <c r="E5" s="189" t="s">
+      <c r="E5" s="181" t="s">
         <v>9</v>
       </c>
-      <c r="F5" s="189" t="s">
+      <c r="F5" s="181" t="s">
         <v>10</v>
       </c>
-      <c r="G5" s="194" t="s">
+      <c r="G5" s="183" t="s">
         <v>97</v>
       </c>
-      <c r="H5" s="194" t="s">
+      <c r="H5" s="183" t="s">
         <v>98</v>
       </c>
       <c r="K5" s="23">
         <f>Project_Start-WEEKDAY(Project_Start,1)+2+7*(Display_Week-1)</f>
-        <v>46251</v>
+        <v>46244</v>
       </c>
       <c r="L5" s="23">
         <f>K5+1</f>
-        <v>46252</v>
+        <v>46245</v>
       </c>
       <c r="M5" s="23">
         <f t="shared" ref="M5:AZ5" si="0">L5+1</f>
-        <v>46253</v>
+        <v>46246</v>
       </c>
       <c r="N5" s="23">
         <f t="shared" si="0"/>
-        <v>46254</v>
+        <v>46247</v>
       </c>
       <c r="O5" s="23">
         <f t="shared" si="0"/>
-        <v>46255</v>
+        <v>46248</v>
       </c>
       <c r="P5" s="23">
         <f t="shared" si="0"/>
-        <v>46256</v>
+        <v>46249</v>
       </c>
       <c r="Q5" s="24">
         <f t="shared" si="0"/>
-        <v>46257</v>
+        <v>46250</v>
       </c>
       <c r="R5" s="25">
         <f>Q5+1</f>
-        <v>46258</v>
+        <v>46251</v>
       </c>
       <c r="S5" s="23">
         <f>R5+1</f>
-        <v>46259</v>
+        <v>46252</v>
       </c>
       <c r="T5" s="23">
         <f t="shared" si="0"/>
-        <v>46260</v>
+        <v>46253</v>
       </c>
       <c r="U5" s="23">
         <f t="shared" si="0"/>
-        <v>46261</v>
+        <v>46254</v>
       </c>
       <c r="V5" s="23">
         <f t="shared" si="0"/>
-        <v>46262</v>
+        <v>46255</v>
       </c>
       <c r="W5" s="23">
         <f t="shared" si="0"/>
-        <v>46263</v>
+        <v>46256</v>
       </c>
       <c r="X5" s="24">
         <f t="shared" si="0"/>
-        <v>46264</v>
+        <v>46257</v>
       </c>
       <c r="Y5" s="25">
         <f>X5+1</f>
-        <v>46265</v>
+        <v>46258</v>
       </c>
       <c r="Z5" s="23">
         <f>Y5+1</f>
-        <v>46266</v>
+        <v>46259</v>
       </c>
       <c r="AA5" s="23">
         <f t="shared" si="0"/>
-        <v>46267</v>
+        <v>46260</v>
       </c>
       <c r="AB5" s="23">
         <f t="shared" si="0"/>
-        <v>46268</v>
+        <v>46261</v>
       </c>
       <c r="AC5" s="23">
         <f t="shared" si="0"/>
-        <v>46269</v>
+        <v>46262</v>
       </c>
       <c r="AD5" s="23">
         <f t="shared" si="0"/>
-        <v>46270</v>
+        <v>46263</v>
       </c>
       <c r="AE5" s="24">
         <f t="shared" si="0"/>
-        <v>46271</v>
+        <v>46264</v>
       </c>
       <c r="AF5" s="25">
         <f>AE5+1</f>
-        <v>46272</v>
+        <v>46265</v>
       </c>
       <c r="AG5" s="23">
         <f>AF5+1</f>
-        <v>46273</v>
+        <v>46266</v>
       </c>
       <c r="AH5" s="23">
         <f t="shared" si="0"/>
-        <v>46274</v>
+        <v>46267</v>
       </c>
       <c r="AI5" s="23">
         <f t="shared" si="0"/>
-        <v>46275</v>
+        <v>46268</v>
       </c>
       <c r="AJ5" s="23">
         <f t="shared" si="0"/>
-        <v>46276</v>
+        <v>46269</v>
       </c>
       <c r="AK5" s="23">
         <f t="shared" si="0"/>
-        <v>46277</v>
+        <v>46270</v>
       </c>
       <c r="AL5" s="24">
         <f t="shared" si="0"/>
-        <v>46278</v>
+        <v>46271</v>
       </c>
       <c r="AM5" s="25">
         <f>AL5+1</f>
-        <v>46279</v>
+        <v>46272</v>
       </c>
       <c r="AN5" s="23">
         <f>AM5+1</f>
-        <v>46280</v>
+        <v>46273</v>
       </c>
       <c r="AO5" s="23">
         <f t="shared" si="0"/>
-        <v>46281</v>
+        <v>46274</v>
       </c>
       <c r="AP5" s="23">
         <f t="shared" si="0"/>
-        <v>46282</v>
+        <v>46275</v>
       </c>
       <c r="AQ5" s="23">
         <f t="shared" si="0"/>
-        <v>46283</v>
+        <v>46276</v>
       </c>
       <c r="AR5" s="23">
         <f t="shared" si="0"/>
-        <v>46284</v>
+        <v>46277</v>
       </c>
       <c r="AS5" s="24">
         <f t="shared" si="0"/>
-        <v>46285</v>
+        <v>46278</v>
       </c>
       <c r="AT5" s="25">
         <f>AS5+1</f>
-        <v>46286</v>
+        <v>46279</v>
       </c>
       <c r="AU5" s="23">
         <f>AT5+1</f>
-        <v>46287</v>
+        <v>46280</v>
       </c>
       <c r="AV5" s="23">
         <f t="shared" si="0"/>
-        <v>46288</v>
+        <v>46281</v>
       </c>
       <c r="AW5" s="23">
         <f t="shared" si="0"/>
-        <v>46289</v>
+        <v>46282</v>
       </c>
       <c r="AX5" s="23">
         <f t="shared" si="0"/>
-        <v>46290</v>
+        <v>46283</v>
       </c>
       <c r="AY5" s="23">
         <f t="shared" si="0"/>
-        <v>46291</v>
+        <v>46284</v>
       </c>
       <c r="AZ5" s="24">
         <f t="shared" si="0"/>
-        <v>46292</v>
+        <v>46285</v>
       </c>
       <c r="BA5" s="25">
         <f>AZ5+1</f>
-        <v>46293</v>
+        <v>46286</v>
       </c>
       <c r="BB5" s="23">
         <f>BA5+1</f>
-        <v>46294</v>
+        <v>46287</v>
       </c>
       <c r="BC5" s="23">
         <f t="shared" ref="BC5:BG5" si="1">BB5+1</f>
-        <v>46295</v>
+        <v>46288</v>
       </c>
       <c r="BD5" s="23">
         <f t="shared" si="1"/>
-        <v>46296</v>
+        <v>46289</v>
       </c>
       <c r="BE5" s="23">
         <f t="shared" si="1"/>
-        <v>46297</v>
+        <v>46290</v>
       </c>
       <c r="BF5" s="23">
         <f t="shared" si="1"/>
-        <v>46298</v>
+        <v>46291</v>
       </c>
       <c r="BG5" s="24">
         <f t="shared" si="1"/>
-        <v>46299</v>
+        <v>46292</v>
       </c>
       <c r="BH5" s="25">
         <f>BG5+1</f>
-        <v>46300</v>
+        <v>46293</v>
       </c>
       <c r="BI5" s="23">
         <f>BH5+1</f>
-        <v>46301</v>
+        <v>46294</v>
       </c>
       <c r="BJ5" s="23">
         <f t="shared" ref="BJ5:BN5" si="2">BI5+1</f>
-        <v>46302</v>
+        <v>46295</v>
       </c>
       <c r="BK5" s="23">
         <f t="shared" si="2"/>
-        <v>46303</v>
+        <v>46296</v>
       </c>
       <c r="BL5" s="23">
         <f t="shared" si="2"/>
-        <v>46304</v>
+        <v>46297</v>
       </c>
       <c r="BM5" s="23">
         <f t="shared" si="2"/>
-        <v>46305</v>
+        <v>46298</v>
       </c>
       <c r="BN5" s="23">
         <f t="shared" si="2"/>
-        <v>46306</v>
+        <v>46299</v>
       </c>
     </row>
     <row r="6" spans="1:66" s="18" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="186"/>
-      <c r="B6" s="188"/>
-      <c r="C6" s="188"/>
-      <c r="D6" s="188"/>
-      <c r="E6" s="190"/>
-      <c r="F6" s="188"/>
-      <c r="G6" s="195"/>
-      <c r="H6" s="195"/>
+      <c r="A6" s="178"/>
+      <c r="B6" s="180"/>
+      <c r="C6" s="180"/>
+      <c r="D6" s="180"/>
+      <c r="E6" s="182"/>
+      <c r="F6" s="180"/>
+      <c r="G6" s="184"/>
+      <c r="H6" s="184"/>
       <c r="K6" s="26" t="str">
         <f t="shared" ref="K6:BN6" si="3">LEFT(TEXT(K5,"ddd"),1)</f>
         <v>l</v>
@@ -3578,7 +3578,7 @@
       <c r="E13" s="89">
         <v>40</v>
       </c>
-      <c r="F13" s="89">
+      <c r="F13" s="77">
         <f>D13+E13</f>
         <v>46306</v>
       </c>
@@ -3658,7 +3658,7 @@
         <v>13</v>
       </c>
       <c r="C14" s="102">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="D14" s="103">
         <v>46265</v>
@@ -3674,7 +3674,7 @@
         <v>12</v>
       </c>
       <c r="H14" s="104">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I14" s="9"/>
       <c r="J14" s="5"/>
@@ -4066,10 +4066,10 @@
         <f>D19+E19</f>
         <v>46258</v>
       </c>
-      <c r="G19" s="192">
+      <c r="G19" s="173">
         <v>4</v>
       </c>
-      <c r="H19" s="192">
+      <c r="H19" s="173">
         <v>4</v>
       </c>
       <c r="I19" s="9"/>
@@ -4149,8 +4149,8 @@
         <f>D20+E20</f>
         <v>46293</v>
       </c>
-      <c r="G20" s="193"/>
-      <c r="H20" s="193"/>
+      <c r="G20" s="174"/>
+      <c r="H20" s="174"/>
       <c r="I20" s="9"/>
       <c r="J20" s="5"/>
       <c r="K20" s="59"/>
@@ -5238,6 +5238,13 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="K1:Q1"/>
+    <mergeCell ref="S1:AB1"/>
+    <mergeCell ref="K2:Q2"/>
+    <mergeCell ref="S2:AB2"/>
+    <mergeCell ref="K4:Q4"/>
+    <mergeCell ref="R4:X4"/>
+    <mergeCell ref="Y4:AE4"/>
     <mergeCell ref="BA4:BG4"/>
     <mergeCell ref="BH4:BN4"/>
     <mergeCell ref="A5:A6"/>
@@ -5251,13 +5258,6 @@
     <mergeCell ref="AT4:AZ4"/>
     <mergeCell ref="G5:G6"/>
     <mergeCell ref="H5:H6"/>
-    <mergeCell ref="K1:Q1"/>
-    <mergeCell ref="S1:AB1"/>
-    <mergeCell ref="K2:Q2"/>
-    <mergeCell ref="S2:AB2"/>
-    <mergeCell ref="K4:Q4"/>
-    <mergeCell ref="R4:X4"/>
-    <mergeCell ref="Y4:AE4"/>
   </mergeCells>
   <conditionalFormatting sqref="C7:C33">
     <cfRule type="dataBar" priority="8">
@@ -5310,7 +5310,7 @@
       <formula>AND(task_end&gt;=K$5,task_start&lt;L$5)</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations disablePrompts="1" count="1">
+  <dataValidations count="1">
     <dataValidation type="whole" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" promptTitle="Display Week" prompt="Changing this number will scroll the Gantt Chart view." sqref="S2" xr:uid="{5055D4DC-4AC9-4908-8988-4E07AB8DE9B0}">
       <formula1>1</formula1>
     </dataValidation>
@@ -5376,7 +5376,7 @@
       </c>
     </row>
     <row r="3" spans="2:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="191" t="s">
+      <c r="B3" s="192" t="s">
         <v>41</v>
       </c>
       <c r="C3" s="151" t="s">
@@ -5390,7 +5390,7 @@
       </c>
     </row>
     <row r="4" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B4" s="191"/>
+      <c r="B4" s="192"/>
       <c r="C4" s="149" t="s">
         <v>43</v>
       </c>
@@ -5402,7 +5402,7 @@
       </c>
     </row>
     <row r="5" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B5" s="191"/>
+      <c r="B5" s="192"/>
       <c r="C5" s="149" t="s">
         <v>44</v>
       </c>
@@ -5414,7 +5414,7 @@
       </c>
     </row>
     <row r="6" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B6" s="191"/>
+      <c r="B6" s="192"/>
       <c r="C6" s="149" t="s">
         <v>45</v>
       </c>
@@ -5426,7 +5426,7 @@
       </c>
     </row>
     <row r="7" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B7" s="191"/>
+      <c r="B7" s="192"/>
       <c r="C7" s="149"/>
       <c r="D7" s="149"/>
       <c r="E7" s="149"/>
@@ -5436,7 +5436,7 @@
       </c>
     </row>
     <row r="8" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B8" s="191"/>
+      <c r="B8" s="192"/>
       <c r="C8" s="149"/>
       <c r="D8" s="149"/>
       <c r="E8" s="149"/>
@@ -5446,7 +5446,7 @@
       </c>
     </row>
     <row r="9" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B9" s="191"/>
+      <c r="B9" s="192"/>
       <c r="C9" s="149"/>
       <c r="D9" s="149"/>
       <c r="E9" s="149"/>
@@ -5456,7 +5456,7 @@
       </c>
     </row>
     <row r="10" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B10" s="191"/>
+      <c r="B10" s="192"/>
       <c r="C10" s="149"/>
       <c r="D10" s="149"/>
       <c r="E10" s="149"/>
@@ -5466,7 +5466,7 @@
       </c>
     </row>
     <row r="11" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B11" s="191"/>
+      <c r="B11" s="192"/>
       <c r="C11" s="149"/>
       <c r="D11" s="149"/>
       <c r="E11" s="149"/>
@@ -5476,7 +5476,7 @@
       </c>
     </row>
     <row r="12" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B12" s="191"/>
+      <c r="B12" s="192"/>
       <c r="C12" s="149"/>
       <c r="D12" s="149"/>
       <c r="E12" s="149"/>
@@ -5486,7 +5486,7 @@
       </c>
     </row>
     <row r="13" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B13" s="191" t="s">
+      <c r="B13" s="192" t="s">
         <v>46</v>
       </c>
       <c r="C13" s="149"/>
@@ -5498,7 +5498,7 @@
       </c>
     </row>
     <row r="14" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B14" s="191"/>
+      <c r="B14" s="192"/>
       <c r="C14" s="149"/>
       <c r="D14" s="149"/>
       <c r="E14" s="149"/>
@@ -5508,7 +5508,7 @@
       </c>
     </row>
     <row r="15" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B15" s="191"/>
+      <c r="B15" s="192"/>
       <c r="C15" s="149"/>
       <c r="D15" s="149"/>
       <c r="E15" s="149"/>
@@ -5518,7 +5518,7 @@
       </c>
     </row>
     <row r="16" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B16" s="191"/>
+      <c r="B16" s="192"/>
       <c r="C16" s="149"/>
       <c r="D16" s="149"/>
       <c r="E16" s="149"/>
@@ -5528,7 +5528,7 @@
       </c>
     </row>
     <row r="17" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B17" s="191"/>
+      <c r="B17" s="192"/>
       <c r="C17" s="149"/>
       <c r="D17" s="149"/>
       <c r="E17" s="149"/>
@@ -5538,7 +5538,7 @@
       </c>
     </row>
     <row r="18" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B18" s="191"/>
+      <c r="B18" s="192"/>
       <c r="C18" s="149"/>
       <c r="D18" s="149"/>
       <c r="E18" s="149"/>
@@ -5548,7 +5548,7 @@
       </c>
     </row>
     <row r="19" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B19" s="191"/>
+      <c r="B19" s="192"/>
       <c r="C19" s="149"/>
       <c r="D19" s="149"/>
       <c r="E19" s="149"/>
@@ -5558,7 +5558,7 @@
       </c>
     </row>
     <row r="20" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B20" s="191"/>
+      <c r="B20" s="192"/>
       <c r="C20" s="149"/>
       <c r="D20" s="149"/>
       <c r="E20" s="149"/>
@@ -5568,7 +5568,7 @@
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B21" s="191"/>
+      <c r="B21" s="192"/>
       <c r="C21" s="149"/>
       <c r="D21" s="149"/>
       <c r="E21" s="149"/>
@@ -5578,7 +5578,7 @@
       </c>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B22" s="191"/>
+      <c r="B22" s="192"/>
       <c r="C22" s="149"/>
       <c r="D22" s="149"/>
       <c r="E22" s="149"/>
@@ -5588,7 +5588,7 @@
       </c>
     </row>
     <row r="23" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B23" s="191"/>
+      <c r="B23" s="192"/>
       <c r="C23" s="149"/>
       <c r="D23" s="149"/>
       <c r="E23" s="149"/>
@@ -5623,14 +5623,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B1" s="173" t="s">
+      <c r="B1" s="193" t="s">
         <v>47</v>
       </c>
-      <c r="C1" s="174"/>
-      <c r="D1" s="174"/>
-      <c r="E1" s="174"/>
-      <c r="F1" s="174"/>
-      <c r="G1" s="175"/>
+      <c r="C1" s="194"/>
+      <c r="D1" s="194"/>
+      <c r="E1" s="194"/>
+      <c r="F1" s="194"/>
+      <c r="G1" s="195"/>
     </row>
     <row r="2" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B2" t="s">
@@ -5817,12 +5817,12 @@
         <f>Tabla1[[#This Row],[Precio unitario]]*Tabla1[[#This Row],[Cantidad]]</f>
         <v>13000</v>
       </c>
-      <c r="L10" s="173"/>
-      <c r="M10" s="174"/>
-      <c r="N10" s="174"/>
-      <c r="O10" s="174"/>
-      <c r="P10" s="174"/>
-      <c r="Q10" s="175"/>
+      <c r="L10" s="193"/>
+      <c r="M10" s="194"/>
+      <c r="N10" s="194"/>
+      <c r="O10" s="194"/>
+      <c r="P10" s="194"/>
+      <c r="Q10" s="195"/>
     </row>
     <row r="11" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B11" s="145" t="s">
@@ -6207,6 +6207,35 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <Image xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
+      <Url xsi:nil="true"/>
+      <Description xsi:nil="true"/>
+    </Image>
+    <Status xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">Not started</Status>
+    <Background xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">false</Background>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <ImageTagsTaxHTField xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </ImageTagsTaxHTField>
+    <TaxCatchAll xmlns="230e9df3-be65-4c73-a93b-d1236ebd677e" xsi:nil="true"/>
+    <MediaServiceKeyPoints xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010079F111ED35F8CC479449609E8A0923A6" ma:contentTypeVersion="28" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="60f5a4f2d2b0abadcf532d48ebf9cb71">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xmlns:ns3="16c05727-aa75-4e4a-9b5f-8a80a1165891" xmlns:ns4="230e9df3-be65-4c73-a93b-d1236ebd677e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="7dd78129e6a1811f84807ad11c651531" ns1:_="" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -6518,36 +6547,27 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A82239A0-E68C-493F-BEE6-C77FEA397FD6}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5"/>
+    <ds:schemaRef ds:uri="230e9df3-be65-4c73-a93b-d1236ebd677e"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <Image xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
-      <Url xsi:nil="true"/>
-      <Description xsi:nil="true"/>
-    </Image>
-    <Status xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">Not started</Status>
-    <Background xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">false</Background>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <ImageTagsTaxHTField xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </ImageTagsTaxHTField>
-    <TaxCatchAll xmlns="230e9df3-be65-4c73-a93b-d1236ebd677e" xsi:nil="true"/>
-    <MediaServiceKeyPoints xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97245281-08F3-4104-84BD-39F3D8CFB195}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A09426A3-87E9-4865-8A6C-3456B026AE03}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -6568,26 +6588,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97245281-08F3-4104-84BD-39F3D8CFB195}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A82239A0-E68C-493F-BEE6-C77FEA397FD6}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5"/>
-    <ds:schemaRef ds:uri="230e9df3-be65-4c73-a93b-d1236ebd677e"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata"/>
 </file>